--- a/src/data/raw/2015 შუალედური პარლამენტი.xlsx
+++ b/src/data/raw/2015 შუალედური პარლამენტი.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox (Personal)\My projects\Elections\ge_elections_dashboard\wireframe\observable_framework\elections_data\src\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BA4C5D4-C74E-4BA9-9C09-CC515BC8F990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25FC924C-2762-453E-893C-D601A0078CDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="11 საგარეჯო" sheetId="3" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId2"/>
+    <sheet name="შედეგები" sheetId="3" r:id="rId1"/>
+    <sheet name="კანდიდატები" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'11 საგარეჯო'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">შედეგები!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,10 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
-  <si>
-    <t>ოლქის N და დასახელება</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="42">
   <si>
     <t>უბნის N</t>
   </si>
@@ -88,19 +85,85 @@
     <t>vote_44</t>
   </si>
   <si>
-    <t>Elections</t>
+    <t>ოლქი</t>
   </si>
   <si>
-    <t>District</t>
+    <t>სახელი</t>
   </si>
   <si>
-    <t>Name</t>
+    <t>გვარი</t>
   </si>
   <si>
-    <t>SMD</t>
+    <t>პარტიის ნომერი</t>
   </si>
   <si>
-    <t>Party</t>
+    <t>პარტიის სახელი</t>
+  </si>
+  <si>
+    <t>ირმა</t>
+  </si>
+  <si>
+    <t>ინაშვილი</t>
+  </si>
+  <si>
+    <t>საქართველოს პატრიოტთა ალიანსი</t>
+  </si>
+  <si>
+    <t>თამარ</t>
+  </si>
+  <si>
+    <t>ხიდაშელი</t>
+  </si>
+  <si>
+    <t>ქართული ოცნება</t>
+  </si>
+  <si>
+    <t>მიხეილ</t>
+  </si>
+  <si>
+    <t>ანდღულაძე</t>
+  </si>
+  <si>
+    <t>გიორგი</t>
+  </si>
+  <si>
+    <t>დავითაია</t>
+  </si>
+  <si>
+    <t>ზურაბ</t>
+  </si>
+  <si>
+    <t>ჯორბენაძე</t>
+  </si>
+  <si>
+    <t>საინიციატივო ჯგუფი</t>
+  </si>
+  <si>
+    <t>ოლქის N</t>
+  </si>
+  <si>
+    <t>ოლქის დასახელება</t>
+  </si>
+  <si>
+    <t>საგარეჯო</t>
+  </si>
+  <si>
+    <t>მარტვილი</t>
+  </si>
+  <si>
+    <t>ეთერ</t>
+  </si>
+  <si>
+    <t>მეძველია</t>
+  </si>
+  <si>
+    <t>სოსო</t>
+  </si>
+  <si>
+    <t>დანელია</t>
+  </si>
+  <si>
+    <t>id</t>
   </si>
 </sst>
 </file>
@@ -170,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -188,7 +251,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -477,1145 +539,1278 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P89"/>
+  <dimension ref="A1:R89"/>
   <sheetFormatPr defaultColWidth="9.07421875" defaultRowHeight="15.9" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="15.84375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="8" style="4" customWidth="1"/>
-    <col min="3" max="3" width="17.4609375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="18.69140625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="22.07421875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.4609375" style="4" customWidth="1"/>
-    <col min="7" max="7" width="13.4609375" style="4" customWidth="1"/>
-    <col min="8" max="8" width="16.07421875" style="4" customWidth="1"/>
-    <col min="9" max="9" width="18.4609375" style="4" customWidth="1"/>
-    <col min="10" max="10" width="6.69140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.4609375" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4" style="4" customWidth="1"/>
-    <col min="13" max="14" width="5.07421875" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.69140625" style="4" customWidth="1"/>
-    <col min="16" max="16" width="6.07421875" style="4" hidden="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.07421875" style="4"/>
+    <col min="1" max="1" width="9.07421875" style="4"/>
+    <col min="2" max="3" width="15.84375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="8" style="4" customWidth="1"/>
+    <col min="5" max="5" width="17.4609375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="18.69140625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="22.07421875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="12.4609375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="13.4609375" style="4" customWidth="1"/>
+    <col min="10" max="10" width="16.07421875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="18.4609375" style="4" customWidth="1"/>
+    <col min="12" max="12" width="6.69140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.4609375" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4" style="4" customWidth="1"/>
+    <col min="15" max="16" width="5.07421875" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.69140625" style="4" customWidth="1"/>
+    <col min="18" max="18" width="6.07421875" style="4" customWidth="1"/>
+    <col min="19" max="16384" width="9.07421875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="2" customFormat="1" ht="47.6" x14ac:dyDescent="0.5">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:18" s="2" customFormat="1" ht="47.6" x14ac:dyDescent="0.5">
+      <c r="A1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="E1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="G1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="R1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A2" s="4">
+        <v>11001</v>
+      </c>
+      <c r="B2" s="3">
+        <v>11</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3">
+        <v>712</v>
+      </c>
+      <c r="G2" s="3">
+        <v>6</v>
+      </c>
+      <c r="H2" s="3">
+        <v>82</v>
+      </c>
+      <c r="I2" s="3">
+        <v>193</v>
+      </c>
+      <c r="J2" s="3">
+        <v>274</v>
+      </c>
+      <c r="K2" s="3">
+        <v>650</v>
+      </c>
+      <c r="L2" s="3">
+        <v>148</v>
+      </c>
+      <c r="M2" s="3">
+        <v>96</v>
+      </c>
+      <c r="N2" s="3">
+        <v>0</v>
+      </c>
+      <c r="O2" s="3">
+        <v>4</v>
+      </c>
+      <c r="P2" s="3">
+        <v>8</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>18</v>
+      </c>
+      <c r="R2" s="8">
+        <f t="shared" ref="R2:R33" si="0">Q2*100/J2</f>
+        <v>6.5693430656934311</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A3" s="4">
+        <v>11002</v>
+      </c>
+      <c r="B3" s="3">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="3">
         <v>2</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E3" s="3"/>
+      <c r="F3" s="3">
+        <v>1207</v>
+      </c>
+      <c r="G3" s="3">
+        <v>5</v>
+      </c>
+      <c r="H3" s="3">
+        <v>135</v>
+      </c>
+      <c r="I3" s="3">
+        <v>350</v>
+      </c>
+      <c r="J3" s="3">
+        <v>450</v>
+      </c>
+      <c r="K3" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L3" s="3">
+        <v>221</v>
+      </c>
+      <c r="M3" s="3">
+        <v>175</v>
+      </c>
+      <c r="N3" s="3">
         <v>3</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" s="6" t="s">
+      <c r="O3" s="3">
         <v>15</v>
       </c>
-      <c r="O1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A2" s="3">
-        <v>11</v>
-      </c>
-      <c r="B2" s="3">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3">
-        <v>712</v>
-      </c>
-      <c r="E2" s="3">
-        <v>6</v>
-      </c>
-      <c r="F2" s="3">
-        <v>82</v>
-      </c>
-      <c r="G2" s="3">
-        <v>193</v>
-      </c>
-      <c r="H2" s="3">
-        <v>274</v>
-      </c>
-      <c r="I2" s="3">
-        <v>650</v>
-      </c>
-      <c r="J2" s="3">
-        <v>148</v>
-      </c>
-      <c r="K2" s="3">
-        <v>96</v>
-      </c>
-      <c r="L2" s="3">
-        <v>0</v>
-      </c>
-      <c r="M2" s="3">
-        <v>4</v>
-      </c>
-      <c r="N2" s="3">
-        <v>8</v>
-      </c>
-      <c r="O2" s="3">
-        <v>18</v>
-      </c>
-      <c r="P2" s="8">
-        <f t="shared" ref="P2:P33" si="0">O2*100/H2</f>
-        <v>6.5693430656934311</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A3" s="3">
-        <v>11</v>
-      </c>
-      <c r="B3" s="3">
-        <v>2</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3">
-        <v>1207</v>
-      </c>
-      <c r="E3" s="3">
-        <v>5</v>
-      </c>
-      <c r="F3" s="3">
-        <v>135</v>
-      </c>
-      <c r="G3" s="3">
-        <v>350</v>
-      </c>
-      <c r="H3" s="3">
-        <v>450</v>
-      </c>
-      <c r="I3" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J3" s="3">
-        <v>221</v>
-      </c>
-      <c r="K3" s="3">
-        <v>175</v>
-      </c>
-      <c r="L3" s="3">
-        <v>3</v>
-      </c>
-      <c r="M3" s="3">
+      <c r="P3" s="3">
         <v>15</v>
       </c>
-      <c r="N3" s="3">
-        <v>15</v>
-      </c>
-      <c r="O3" s="3">
+      <c r="Q3" s="3">
         <v>21</v>
       </c>
-      <c r="P3" s="8">
+      <c r="R3" s="8">
         <f t="shared" si="0"/>
         <v>4.666666666666667</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A4" s="3">
-        <v>11</v>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A4" s="4">
+        <v>11003</v>
       </c>
       <c r="B4" s="3">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="3">
         <v>3</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3">
+      <c r="E4" s="3"/>
+      <c r="F4" s="3">
         <v>1103</v>
       </c>
-      <c r="E4" s="3">
+      <c r="G4" s="3">
         <v>10</v>
       </c>
-      <c r="F4" s="3">
+      <c r="H4" s="3">
         <v>130</v>
       </c>
-      <c r="G4" s="3">
+      <c r="I4" s="3">
         <v>312</v>
       </c>
-      <c r="H4" s="3">
+      <c r="J4" s="3">
         <v>404</v>
       </c>
-      <c r="I4" s="3">
+      <c r="K4" s="3">
         <v>1050</v>
       </c>
-      <c r="J4" s="3">
+      <c r="L4" s="3">
         <v>198</v>
       </c>
-      <c r="K4" s="3">
+      <c r="M4" s="3">
         <v>166</v>
       </c>
-      <c r="L4" s="3">
+      <c r="N4" s="3">
         <v>0</v>
       </c>
-      <c r="M4" s="3">
+      <c r="O4" s="3">
         <v>4</v>
       </c>
-      <c r="N4" s="3">
-        <v>11</v>
-      </c>
-      <c r="O4" s="3">
+      <c r="P4" s="3">
+        <v>11</v>
+      </c>
+      <c r="Q4" s="3">
         <v>25</v>
       </c>
-      <c r="P4" s="8">
+      <c r="R4" s="8">
         <f t="shared" si="0"/>
         <v>6.1881188118811883</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A5" s="3">
-        <v>11</v>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A5" s="4">
+        <v>11004</v>
       </c>
       <c r="B5" s="3">
+        <v>11</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="3">
         <v>4</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3">
+      <c r="E5" s="3"/>
+      <c r="F5" s="3">
         <v>827</v>
       </c>
-      <c r="E5" s="3">
+      <c r="G5" s="3">
         <v>8</v>
       </c>
-      <c r="F5" s="3">
+      <c r="H5" s="3">
         <v>104</v>
       </c>
-      <c r="G5" s="3">
+      <c r="I5" s="3">
         <v>246</v>
       </c>
-      <c r="H5" s="3">
+      <c r="J5" s="3">
         <v>319</v>
       </c>
-      <c r="I5" s="3">
+      <c r="K5" s="3">
         <v>750</v>
       </c>
-      <c r="J5" s="3">
+      <c r="L5" s="3">
         <v>203</v>
       </c>
-      <c r="K5" s="3">
+      <c r="M5" s="3">
         <v>99</v>
       </c>
-      <c r="L5" s="3">
+      <c r="N5" s="3">
         <v>0</v>
       </c>
-      <c r="M5" s="3">
+      <c r="O5" s="3">
         <v>5</v>
       </c>
-      <c r="N5" s="3">
+      <c r="P5" s="3">
         <v>3</v>
       </c>
-      <c r="O5" s="3">
+      <c r="Q5" s="3">
         <v>9</v>
       </c>
-      <c r="P5" s="8">
+      <c r="R5" s="8">
         <f t="shared" si="0"/>
         <v>2.8213166144200628</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A6" s="3">
-        <v>11</v>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A6" s="4">
+        <v>11005</v>
       </c>
       <c r="B6" s="3">
+        <v>11</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="3">
         <v>5</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3">
+      <c r="E6" s="3"/>
+      <c r="F6" s="3">
         <v>692</v>
       </c>
-      <c r="E6" s="3">
+      <c r="G6" s="3">
         <v>8</v>
       </c>
-      <c r="F6" s="3">
+      <c r="H6" s="3">
         <v>78</v>
       </c>
-      <c r="G6" s="3">
+      <c r="I6" s="3">
         <v>197</v>
       </c>
-      <c r="H6" s="3">
+      <c r="J6" s="3">
         <v>239</v>
       </c>
-      <c r="I6" s="3">
+      <c r="K6" s="3">
         <v>650</v>
       </c>
-      <c r="J6" s="3">
+      <c r="L6" s="3">
         <v>140</v>
       </c>
-      <c r="K6" s="3">
+      <c r="M6" s="3">
         <v>86</v>
       </c>
-      <c r="L6" s="3">
+      <c r="N6" s="3">
         <v>0</v>
       </c>
-      <c r="M6" s="3">
+      <c r="O6" s="3">
         <v>2</v>
       </c>
-      <c r="N6" s="3">
+      <c r="P6" s="3">
         <v>1</v>
       </c>
-      <c r="O6" s="3">
+      <c r="Q6" s="3">
         <v>10</v>
       </c>
-      <c r="P6" s="8">
+      <c r="R6" s="8">
         <f t="shared" si="0"/>
         <v>4.1841004184100417</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A7" s="3">
-        <v>11</v>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A7" s="4">
+        <v>11006</v>
       </c>
       <c r="B7" s="3">
+        <v>11</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="3">
         <v>6</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3">
+      <c r="E7" s="3"/>
+      <c r="F7" s="3">
         <v>1380</v>
       </c>
-      <c r="E7" s="3">
+      <c r="G7" s="3">
         <v>7</v>
       </c>
-      <c r="F7" s="3">
+      <c r="H7" s="3">
         <v>157</v>
       </c>
-      <c r="G7" s="3">
+      <c r="I7" s="3">
         <v>430</v>
       </c>
-      <c r="H7" s="3">
+      <c r="J7" s="3">
         <v>537</v>
       </c>
-      <c r="I7" s="3">
+      <c r="K7" s="3">
         <v>1300</v>
       </c>
-      <c r="J7" s="3">
+      <c r="L7" s="3">
         <v>334</v>
       </c>
-      <c r="K7" s="3">
+      <c r="M7" s="3">
         <v>169</v>
       </c>
-      <c r="L7" s="3">
+      <c r="N7" s="3">
         <v>0</v>
       </c>
-      <c r="M7" s="3">
+      <c r="O7" s="3">
         <v>3</v>
       </c>
-      <c r="N7" s="3">
+      <c r="P7" s="3">
         <v>8</v>
       </c>
-      <c r="O7" s="3">
+      <c r="Q7" s="3">
         <v>23</v>
       </c>
-      <c r="P7" s="8">
+      <c r="R7" s="8">
         <f t="shared" si="0"/>
         <v>4.2830540037243949</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A8" s="3">
-        <v>11</v>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A8" s="4">
+        <v>11007</v>
       </c>
       <c r="B8" s="3">
+        <v>11</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="3">
         <v>7</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3">
+      <c r="E8" s="3"/>
+      <c r="F8" s="3">
         <v>929</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>6</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>93</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>226</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>272</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>850</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>133</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>106</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>2</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>17</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>13</v>
       </c>
-      <c r="P8" s="8">
+      <c r="R8" s="8">
         <f t="shared" si="0"/>
         <v>4.7794117647058822</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A9" s="3">
-        <v>11</v>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A9" s="4">
+        <v>11008</v>
       </c>
       <c r="B9" s="3">
+        <v>11</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="3">
         <v>8</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3">
+      <c r="E9" s="3"/>
+      <c r="F9" s="3">
         <v>1198</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>4</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>116</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>290</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>381</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>261</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>91</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>2</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>0</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>14</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>13</v>
       </c>
-      <c r="P9" s="8">
+      <c r="R9" s="8">
         <f t="shared" si="0"/>
         <v>3.4120734908136483</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A10" s="3">
-        <v>11</v>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A10" s="4">
+        <v>11009</v>
       </c>
       <c r="B10" s="3">
+        <v>11</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="3">
         <v>9</v>
       </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3">
+      <c r="E10" s="3"/>
+      <c r="F10" s="3">
         <v>982</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>6</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>93</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>277</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>368</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>950</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>261</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>81</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>1</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>7</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>5</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>13</v>
       </c>
-      <c r="P10" s="8">
+      <c r="R10" s="8">
         <f t="shared" si="0"/>
         <v>3.5326086956521738</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A11" s="3">
-        <v>11</v>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A11" s="4">
+        <v>11010</v>
       </c>
       <c r="B11" s="3">
+        <v>11</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="3">
         <v>10</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3">
+      <c r="E11" s="3"/>
+      <c r="F11" s="3">
         <v>1042</v>
       </c>
-      <c r="E11" s="3">
+      <c r="G11" s="3">
         <v>3</v>
       </c>
-      <c r="F11" s="3">
+      <c r="H11" s="3">
         <v>97</v>
       </c>
-      <c r="G11" s="3">
+      <c r="I11" s="3">
         <v>274</v>
       </c>
-      <c r="H11" s="3">
+      <c r="J11" s="3">
         <v>339</v>
       </c>
-      <c r="I11" s="3">
+      <c r="K11" s="3">
         <v>950</v>
       </c>
-      <c r="J11" s="3">
+      <c r="L11" s="3">
         <v>151</v>
       </c>
-      <c r="K11" s="3">
+      <c r="M11" s="3">
         <v>142</v>
       </c>
-      <c r="L11" s="3">
+      <c r="N11" s="3">
         <v>4</v>
       </c>
-      <c r="M11" s="3">
+      <c r="O11" s="3">
         <v>2</v>
       </c>
-      <c r="N11" s="3">
+      <c r="P11" s="3">
         <v>13</v>
       </c>
-      <c r="O11" s="3">
+      <c r="Q11" s="3">
         <v>27</v>
       </c>
-      <c r="P11" s="8">
+      <c r="R11" s="8">
         <f t="shared" si="0"/>
         <v>7.9646017699115044</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A12" s="3">
-        <v>11</v>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A12" s="4">
+        <v>11011</v>
       </c>
       <c r="B12" s="3">
         <v>11</v>
       </c>
-      <c r="C12" s="3"/>
+      <c r="C12" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="D12" s="3">
+        <v>11</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3">
         <v>812</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>1</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>94</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>273</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>331</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>750</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>172</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>141</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>3</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>3</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>1</v>
       </c>
-      <c r="O12" s="3">
-        <v>11</v>
-      </c>
-      <c r="P12" s="8">
+      <c r="Q12" s="3">
+        <v>11</v>
+      </c>
+      <c r="R12" s="8">
         <f t="shared" si="0"/>
         <v>3.3232628398791539</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A13" s="3">
-        <v>11</v>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A13" s="4">
+        <v>11012</v>
       </c>
       <c r="B13" s="3">
+        <v>11</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="3">
         <v>12</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3">
+      <c r="E13" s="3"/>
+      <c r="F13" s="3">
         <v>274</v>
       </c>
-      <c r="E13" s="3">
+      <c r="G13" s="3">
         <v>2</v>
       </c>
-      <c r="F13" s="3">
+      <c r="H13" s="3">
         <v>72</v>
       </c>
-      <c r="G13" s="3">
+      <c r="I13" s="3">
         <v>145</v>
       </c>
-      <c r="H13" s="3">
+      <c r="J13" s="3">
         <v>166</v>
       </c>
-      <c r="I13" s="3">
+      <c r="K13" s="3">
         <v>300</v>
       </c>
-      <c r="J13" s="3">
+      <c r="L13" s="3">
         <v>98</v>
       </c>
-      <c r="K13" s="3">
+      <c r="M13" s="3">
         <v>61</v>
       </c>
-      <c r="L13" s="3">
+      <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3">
+      <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3">
+      <c r="P13" s="3">
         <v>1</v>
       </c>
-      <c r="O13" s="3">
+      <c r="Q13" s="3">
         <v>6</v>
       </c>
-      <c r="P13" s="8">
+      <c r="R13" s="8">
         <f t="shared" si="0"/>
         <v>3.6144578313253013</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A14" s="3">
-        <v>11</v>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A14" s="4">
+        <v>11013</v>
       </c>
       <c r="B14" s="3">
+        <v>11</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="3">
         <v>13</v>
       </c>
-      <c r="C14" s="7">
+      <c r="E14" s="7">
         <v>50</v>
       </c>
-      <c r="D14" s="3">
+      <c r="F14" s="3">
         <v>352</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>621</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>399</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>766</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>798</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>1000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>101</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>573</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>9</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>33</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>24</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>59</v>
       </c>
-      <c r="P14" s="8">
+      <c r="R14" s="8">
         <f t="shared" si="0"/>
         <v>7.3934837092731831</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A15" s="3">
-        <v>11</v>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A15" s="4">
+        <v>11014</v>
       </c>
       <c r="B15" s="3">
+        <v>11</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="3">
         <v>14</v>
       </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3">
+      <c r="E15" s="3"/>
+      <c r="F15" s="3">
         <v>1286</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>1</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>130</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>296</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>364</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>1250</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>227</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>86</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>3</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>7</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>21</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>20</v>
       </c>
-      <c r="P15" s="8">
+      <c r="R15" s="8">
         <f t="shared" si="0"/>
         <v>5.4945054945054945</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A16" s="3">
-        <v>11</v>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A16" s="4">
+        <v>11015</v>
       </c>
       <c r="B16" s="3">
+        <v>11</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="3">
         <v>15</v>
       </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3">
+      <c r="E16" s="3"/>
+      <c r="F16" s="3">
         <v>942</v>
       </c>
-      <c r="E16" s="3">
+      <c r="G16" s="3">
         <v>6</v>
       </c>
-      <c r="F16" s="3">
+      <c r="H16" s="3">
         <v>112</v>
       </c>
-      <c r="G16" s="3">
+      <c r="I16" s="3">
         <v>290</v>
       </c>
-      <c r="H16" s="3">
+      <c r="J16" s="3">
         <v>364</v>
       </c>
-      <c r="I16" s="3">
+      <c r="K16" s="3">
         <v>900</v>
       </c>
-      <c r="J16" s="3">
+      <c r="L16" s="3">
         <v>224</v>
       </c>
-      <c r="K16" s="3">
+      <c r="M16" s="3">
         <v>125</v>
-      </c>
-      <c r="L16" s="3">
-        <v>2</v>
-      </c>
-      <c r="M16" s="3">
-        <v>2</v>
       </c>
       <c r="N16" s="3">
         <v>2</v>
       </c>
       <c r="O16" s="3">
+        <v>2</v>
+      </c>
+      <c r="P16" s="3">
+        <v>2</v>
+      </c>
+      <c r="Q16" s="3">
         <v>9</v>
       </c>
-      <c r="P16" s="8">
+      <c r="R16" s="8">
         <f t="shared" si="0"/>
         <v>2.4725274725274726</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A17" s="3">
-        <v>11</v>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A17" s="4">
+        <v>11016</v>
       </c>
       <c r="B17" s="3">
+        <v>11</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="3">
         <v>16</v>
       </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3">
+      <c r="E17" s="3"/>
+      <c r="F17" s="3">
         <v>1395</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>181</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>395</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>526</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1350</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>334</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>156</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2</v>
       </c>
-      <c r="N17" s="3">
-        <v>11</v>
-      </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
+        <v>11</v>
+      </c>
+      <c r="Q17" s="3">
         <v>22</v>
       </c>
-      <c r="P17" s="8">
+      <c r="R17" s="8">
         <f t="shared" si="0"/>
         <v>4.1825095057034218</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A18" s="3">
-        <v>11</v>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A18" s="4">
+        <v>11017</v>
       </c>
       <c r="B18" s="3">
+        <v>11</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" s="3">
         <v>17</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3">
+      <c r="E18" s="3"/>
+      <c r="F18" s="3">
         <v>581</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>5</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>103</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>196</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>218</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>550</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>102</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>93</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>1</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>5</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>3</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>14</v>
       </c>
-      <c r="P18" s="8">
+      <c r="R18" s="8">
         <f t="shared" si="0"/>
         <v>6.4220183486238529</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A19" s="3">
-        <v>11</v>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A19" s="4">
+        <v>11018</v>
       </c>
       <c r="B19" s="3">
+        <v>11</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="3">
         <v>18</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3">
+      <c r="E19" s="3"/>
+      <c r="F19" s="3">
         <v>779</v>
       </c>
-      <c r="E19" s="3">
+      <c r="G19" s="3">
         <v>8</v>
       </c>
-      <c r="F19" s="3">
+      <c r="H19" s="3">
         <v>88</v>
       </c>
-      <c r="G19" s="3">
+      <c r="I19" s="3">
         <v>226</v>
       </c>
-      <c r="H19" s="3">
+      <c r="J19" s="3">
         <v>257</v>
       </c>
-      <c r="I19" s="3">
+      <c r="K19" s="3">
         <v>700</v>
       </c>
-      <c r="J19" s="3">
+      <c r="L19" s="3">
         <v>136</v>
       </c>
-      <c r="K19" s="3">
+      <c r="M19" s="3">
         <v>93</v>
       </c>
-      <c r="L19" s="3">
+      <c r="N19" s="3">
         <v>1</v>
       </c>
-      <c r="M19" s="3">
+      <c r="O19" s="3">
         <v>4</v>
       </c>
-      <c r="N19" s="3">
+      <c r="P19" s="3">
         <v>16</v>
       </c>
-      <c r="O19" s="3">
+      <c r="Q19" s="3">
         <v>7</v>
       </c>
-      <c r="P19" s="8">
+      <c r="R19" s="8">
         <f t="shared" si="0"/>
         <v>2.7237354085603114</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A20" s="3">
-        <v>11</v>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A20" s="4">
+        <v>11019</v>
       </c>
       <c r="B20" s="3">
+        <v>11</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="3">
         <v>19</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3">
+      <c r="E20" s="3"/>
+      <c r="F20" s="3">
         <v>910</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>4</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>91</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>234</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>307</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>850</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>171</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>114</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>0</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>6</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>9</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>0</v>
       </c>
-      <c r="P20" s="8">
+      <c r="R20" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A21" s="3">
-        <v>11</v>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A21" s="4">
+        <v>11020</v>
       </c>
       <c r="B21" s="3">
+        <v>11</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="3">
         <v>20</v>
       </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3">
+      <c r="E21" s="3"/>
+      <c r="F21" s="3">
         <v>1177</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>5</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>150</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>384</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>546</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>1150</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>265</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>218</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>3</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>4</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>39</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>17</v>
       </c>
-      <c r="P21" s="8">
+      <c r="R21" s="8">
         <f t="shared" si="0"/>
         <v>3.1135531135531136</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A22" s="3">
-        <v>11</v>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A22" s="4">
+        <v>11021</v>
       </c>
       <c r="B22" s="3">
+        <v>11</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="3">
         <v>21</v>
       </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3">
+      <c r="E22" s="3"/>
+      <c r="F22" s="3">
         <v>839</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>5</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>103</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>236</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>299</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>126</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>138</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>1</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>2</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>16</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>16</v>
       </c>
-      <c r="P22" s="8">
+      <c r="R22" s="8">
         <f t="shared" si="0"/>
         <v>5.3511705685618729</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A23" s="3">
-        <v>11</v>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A23" s="4">
+        <v>11022</v>
       </c>
       <c r="B23" s="3">
+        <v>11</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" s="3">
         <v>22</v>
       </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3">
+      <c r="E23" s="3"/>
+      <c r="F23" s="3">
         <v>82</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>10</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>17</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>28</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>38</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>18</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>20</v>
-      </c>
-      <c r="L23" s="3">
-        <v>0</v>
-      </c>
-      <c r="M23" s="3">
-        <v>0</v>
       </c>
       <c r="N23" s="3">
         <v>0</v>
@@ -1623,2703 +1818,3105 @@
       <c r="O23" s="3">
         <v>0</v>
       </c>
-      <c r="P23" s="8">
+      <c r="P23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>0</v>
+      </c>
+      <c r="R23" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A24" s="3">
-        <v>11</v>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A24" s="4">
+        <v>11023</v>
       </c>
       <c r="B24" s="3">
+        <v>11</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" s="3">
         <v>23</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3">
+      <c r="E24" s="3"/>
+      <c r="F24" s="3">
         <v>94</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>5</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>26</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>51</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>64</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
-        <v>35</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
+        <v>35</v>
+      </c>
+      <c r="M24" s="3">
         <v>26</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
-        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3">
         <v>0</v>
       </c>
-      <c r="P24" s="8">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A25" s="3">
-        <v>11</v>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A25" s="4">
+        <v>11024</v>
       </c>
       <c r="B25" s="3">
+        <v>11</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="3">
         <v>24</v>
       </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3">
+      <c r="E25" s="3"/>
+      <c r="F25" s="3">
         <v>850</v>
       </c>
-      <c r="E25" s="3">
+      <c r="G25" s="3">
         <v>2</v>
       </c>
-      <c r="F25" s="3">
+      <c r="H25" s="3">
         <v>118</v>
       </c>
-      <c r="G25" s="3">
+      <c r="I25" s="3">
         <v>280</v>
       </c>
-      <c r="H25" s="3">
+      <c r="J25" s="3">
         <v>394</v>
       </c>
-      <c r="I25" s="3">
+      <c r="K25" s="3">
         <v>800</v>
       </c>
-      <c r="J25" s="3">
+      <c r="L25" s="3">
         <v>155</v>
       </c>
-      <c r="K25" s="3">
+      <c r="M25" s="3">
         <v>223</v>
-      </c>
-      <c r="L25" s="3">
-        <v>1</v>
-      </c>
-      <c r="M25" s="3">
-        <v>6</v>
       </c>
       <c r="N25" s="3">
         <v>1</v>
       </c>
       <c r="O25" s="3">
+        <v>6</v>
+      </c>
+      <c r="P25" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="3">
         <v>8</v>
       </c>
-      <c r="P25" s="8">
+      <c r="R25" s="8">
         <f t="shared" si="0"/>
         <v>2.030456852791878</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A26" s="3">
-        <v>11</v>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A26" s="4">
+        <v>11025</v>
       </c>
       <c r="B26" s="3">
+        <v>11</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" s="3">
         <v>25</v>
       </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3">
+      <c r="E26" s="3"/>
+      <c r="F26" s="3">
         <v>812</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>4</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>102</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>223</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>259</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>750</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>159</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>79</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>0</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>4</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>4</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>13</v>
       </c>
-      <c r="P26" s="8">
+      <c r="R26" s="8">
         <f t="shared" si="0"/>
         <v>5.019305019305019</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A27" s="3">
-        <v>11</v>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A27" s="4">
+        <v>11026</v>
       </c>
       <c r="B27" s="3">
+        <v>11</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" s="3">
         <v>26</v>
       </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3">
+      <c r="E27" s="3"/>
+      <c r="F27" s="3">
         <v>1091</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>10</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>91</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>223</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>317</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>1050</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>226</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>57</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>1</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>8</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>14</v>
       </c>
-      <c r="O27" s="3">
-        <v>11</v>
-      </c>
-      <c r="P27" s="8">
+      <c r="Q27" s="3">
+        <v>11</v>
+      </c>
+      <c r="R27" s="8">
         <f t="shared" si="0"/>
         <v>3.4700315457413251</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A28" s="3">
-        <v>11</v>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A28" s="4">
+        <v>11027</v>
       </c>
       <c r="B28" s="3">
+        <v>11</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" s="3">
         <v>27</v>
       </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3">
+      <c r="E28" s="3"/>
+      <c r="F28" s="3">
         <v>532</v>
       </c>
-      <c r="E28" s="3">
+      <c r="G28" s="3">
         <v>4</v>
       </c>
-      <c r="F28" s="3">
+      <c r="H28" s="3">
         <v>60</v>
       </c>
-      <c r="G28" s="3">
+      <c r="I28" s="3">
         <v>137</v>
       </c>
-      <c r="H28" s="3">
+      <c r="J28" s="3">
         <v>166</v>
       </c>
-      <c r="I28" s="3">
+      <c r="K28" s="3">
         <v>500</v>
       </c>
-      <c r="J28" s="3">
+      <c r="L28" s="3">
         <v>114</v>
       </c>
-      <c r="K28" s="3">
+      <c r="M28" s="3">
         <v>39</v>
-      </c>
-      <c r="L28" s="3">
-        <v>0</v>
-      </c>
-      <c r="M28" s="3">
-        <v>10</v>
       </c>
       <c r="N28" s="3">
         <v>0</v>
       </c>
       <c r="O28" s="3">
+        <v>10</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
         <v>3</v>
       </c>
-      <c r="P28" s="8">
+      <c r="R28" s="8">
         <f t="shared" si="0"/>
         <v>1.8072289156626506</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A29" s="3">
-        <v>11</v>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A29" s="4">
+        <v>11028</v>
       </c>
       <c r="B29" s="3">
+        <v>11</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" s="3">
         <v>28</v>
       </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3">
+      <c r="E29" s="3"/>
+      <c r="F29" s="3">
         <v>788</v>
       </c>
-      <c r="E29" s="3">
+      <c r="G29" s="3">
         <v>2</v>
       </c>
-      <c r="F29" s="3">
+      <c r="H29" s="3">
         <v>130</v>
       </c>
-      <c r="G29" s="3">
+      <c r="I29" s="3">
         <v>344</v>
       </c>
-      <c r="H29" s="3">
+      <c r="J29" s="3">
         <v>451</v>
       </c>
-      <c r="I29" s="3">
+      <c r="K29" s="3">
         <v>750</v>
       </c>
-      <c r="J29" s="3">
+      <c r="L29" s="3">
         <v>164</v>
       </c>
-      <c r="K29" s="3">
+      <c r="M29" s="3">
         <v>239</v>
       </c>
-      <c r="L29" s="3">
+      <c r="N29" s="3">
         <v>1</v>
       </c>
-      <c r="M29" s="3">
+      <c r="O29" s="3">
         <v>14</v>
       </c>
-      <c r="N29" s="3">
+      <c r="P29" s="3">
         <v>8</v>
       </c>
-      <c r="O29" s="3">
+      <c r="Q29" s="3">
         <v>24</v>
       </c>
-      <c r="P29" s="8">
+      <c r="R29" s="8">
         <f t="shared" si="0"/>
         <v>5.3215077605321506</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A30" s="3">
-        <v>11</v>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A30" s="4">
+        <v>11029</v>
       </c>
       <c r="B30" s="3">
+        <v>11</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30" s="3">
         <v>29</v>
       </c>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3">
+      <c r="E30" s="3"/>
+      <c r="F30" s="3">
         <v>749</v>
       </c>
-      <c r="E30" s="3">
+      <c r="G30" s="3">
         <v>2</v>
       </c>
-      <c r="F30" s="3">
+      <c r="H30" s="3">
         <v>171</v>
       </c>
-      <c r="G30" s="3">
+      <c r="I30" s="3">
         <v>396</v>
       </c>
-      <c r="H30" s="3">
+      <c r="J30" s="3">
         <v>485</v>
       </c>
-      <c r="I30" s="3">
+      <c r="K30" s="3">
         <v>700</v>
       </c>
-      <c r="J30" s="3">
+      <c r="L30" s="3">
         <v>170</v>
       </c>
-      <c r="K30" s="3">
+      <c r="M30" s="3">
         <v>214</v>
       </c>
-      <c r="L30" s="3">
+      <c r="N30" s="3">
         <v>1</v>
       </c>
-      <c r="M30" s="3">
+      <c r="O30" s="3">
         <v>22</v>
       </c>
-      <c r="N30" s="3">
+      <c r="P30" s="3">
         <v>17</v>
       </c>
-      <c r="O30" s="3">
+      <c r="Q30" s="3">
         <v>59</v>
       </c>
-      <c r="P30" s="8">
+      <c r="R30" s="8">
         <f t="shared" si="0"/>
         <v>12.164948453608247</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A31" s="3">
-        <v>11</v>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A31" s="4">
+        <v>11030</v>
       </c>
       <c r="B31" s="3">
+        <v>11</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31" s="3">
         <v>30</v>
       </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3">
+      <c r="E31" s="3"/>
+      <c r="F31" s="3">
         <v>1283</v>
       </c>
-      <c r="E31" s="3">
+      <c r="G31" s="3">
         <v>3</v>
       </c>
-      <c r="F31" s="3">
+      <c r="H31" s="3">
         <v>127</v>
       </c>
-      <c r="G31" s="3">
+      <c r="I31" s="3">
         <v>333</v>
       </c>
-      <c r="H31" s="3">
+      <c r="J31" s="3">
         <v>435</v>
       </c>
-      <c r="I31" s="3">
+      <c r="K31" s="3">
         <v>1250</v>
       </c>
-      <c r="J31" s="3">
+      <c r="L31" s="3">
         <v>264</v>
       </c>
-      <c r="K31" s="3">
+      <c r="M31" s="3">
         <v>151</v>
       </c>
-      <c r="L31" s="3">
+      <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3">
+      <c r="O31" s="3">
         <v>2</v>
       </c>
-      <c r="N31" s="3">
+      <c r="P31" s="3">
         <v>10</v>
       </c>
-      <c r="O31" s="3">
+      <c r="Q31" s="3">
         <v>8</v>
       </c>
-      <c r="P31" s="8">
+      <c r="R31" s="8">
         <f t="shared" si="0"/>
         <v>1.8390804597701149</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A32" s="3">
-        <v>11</v>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A32" s="4">
+        <v>11031</v>
       </c>
       <c r="B32" s="3">
+        <v>11</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" s="3">
         <v>31</v>
       </c>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3">
+      <c r="E32" s="3"/>
+      <c r="F32" s="3">
         <v>1320</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>5</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>164</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>368</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>462</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>1300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>279</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>153</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>0</v>
       </c>
-      <c r="M32" s="3">
-        <v>11</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
+        <v>11</v>
+      </c>
+      <c r="P32" s="3">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
-        <v>11</v>
-      </c>
-      <c r="P32" s="8">
+      <c r="Q32" s="3">
+        <v>11</v>
+      </c>
+      <c r="R32" s="8">
         <f t="shared" si="0"/>
         <v>2.3809523809523809</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A33" s="3">
-        <v>11</v>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A33" s="4">
+        <v>11032</v>
       </c>
       <c r="B33" s="3">
+        <v>11</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D33" s="3">
         <v>32</v>
       </c>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3">
+      <c r="E33" s="3"/>
+      <c r="F33" s="3">
         <v>336</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>5</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>104</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>185</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>202</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>350</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>97</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>98</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>0</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>4</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>1</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>2</v>
       </c>
-      <c r="P33" s="8">
+      <c r="R33" s="8">
         <f t="shared" si="0"/>
         <v>0.99009900990099009</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A34" s="3">
-        <v>11</v>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A34" s="4">
+        <v>11033</v>
       </c>
       <c r="B34" s="3">
+        <v>11</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D34" s="3">
         <v>33</v>
       </c>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3">
+      <c r="E34" s="3"/>
+      <c r="F34" s="3">
         <v>938</v>
       </c>
-      <c r="E34" s="3">
+      <c r="G34" s="3">
         <v>1</v>
       </c>
-      <c r="F34" s="3">
+      <c r="H34" s="3">
         <v>175</v>
       </c>
-      <c r="G34" s="3">
+      <c r="I34" s="3">
         <v>347</v>
       </c>
-      <c r="H34" s="3">
+      <c r="J34" s="3">
         <v>447</v>
       </c>
-      <c r="I34" s="3">
+      <c r="K34" s="3">
         <v>900</v>
       </c>
-      <c r="J34" s="3">
+      <c r="L34" s="3">
         <v>169</v>
       </c>
-      <c r="K34" s="3">
+      <c r="M34" s="3">
         <v>262</v>
       </c>
-      <c r="L34" s="3">
+      <c r="N34" s="3">
         <v>3</v>
       </c>
-      <c r="M34" s="3">
+      <c r="O34" s="3">
         <v>2</v>
       </c>
-      <c r="N34" s="3">
+      <c r="P34" s="3">
         <v>2</v>
       </c>
-      <c r="O34" s="3">
+      <c r="Q34" s="3">
         <v>9</v>
       </c>
-      <c r="P34" s="8">
-        <f t="shared" ref="P34:P50" si="1">O34*100/H34</f>
+      <c r="R34" s="8">
+        <f t="shared" ref="R34:R50" si="1">Q34*100/J34</f>
         <v>2.0134228187919465</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A35" s="3">
-        <v>11</v>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A35" s="4">
+        <v>11034</v>
       </c>
       <c r="B35" s="3">
+        <v>11</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D35" s="3">
         <v>34</v>
       </c>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3">
+      <c r="E35" s="3"/>
+      <c r="F35" s="3">
         <v>1236</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>4</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>180</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>482</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>609</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>1200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>249</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>325</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>4</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>5</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>12</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>14</v>
       </c>
-      <c r="P35" s="8">
+      <c r="R35" s="8">
         <f t="shared" si="1"/>
         <v>2.2988505747126435</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A36" s="3">
-        <v>11</v>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A36" s="4">
+        <v>11035</v>
       </c>
       <c r="B36" s="3">
-        <v>35</v>
-      </c>
-      <c r="C36" s="3"/>
+        <v>11</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="D36" s="3">
+        <v>35</v>
+      </c>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3">
         <v>498</v>
       </c>
-      <c r="E36" s="3">
+      <c r="G36" s="3">
         <v>4</v>
       </c>
-      <c r="F36" s="3">
+      <c r="H36" s="3">
         <v>100</v>
       </c>
-      <c r="G36" s="3">
+      <c r="I36" s="3">
         <v>230</v>
       </c>
-      <c r="H36" s="3">
+      <c r="J36" s="3">
         <v>296</v>
       </c>
-      <c r="I36" s="3">
+      <c r="K36" s="3">
         <v>500</v>
       </c>
-      <c r="J36" s="3">
+      <c r="L36" s="3">
         <v>138</v>
       </c>
-      <c r="K36" s="3">
+      <c r="M36" s="3">
         <v>136</v>
       </c>
-      <c r="L36" s="3">
+      <c r="N36" s="3">
         <v>3</v>
       </c>
-      <c r="M36" s="3">
+      <c r="O36" s="3">
         <v>3</v>
       </c>
-      <c r="N36" s="3">
+      <c r="P36" s="3">
         <v>5</v>
       </c>
-      <c r="O36" s="3">
-        <v>11</v>
-      </c>
-      <c r="P36" s="8">
+      <c r="Q36" s="3">
+        <v>11</v>
+      </c>
+      <c r="R36" s="8">
         <f t="shared" si="1"/>
         <v>3.7162162162162162</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A37" s="3">
-        <v>11</v>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A37" s="4">
+        <v>11036</v>
       </c>
       <c r="B37" s="3">
+        <v>11</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D37" s="3">
         <v>36</v>
       </c>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3">
+      <c r="E37" s="3"/>
+      <c r="F37" s="3">
         <v>415</v>
       </c>
-      <c r="E37" s="3">
+      <c r="G37" s="3">
         <v>1</v>
       </c>
-      <c r="F37" s="3">
+      <c r="H37" s="3">
         <v>79</v>
       </c>
-      <c r="G37" s="3">
+      <c r="I37" s="3">
         <v>179</v>
       </c>
-      <c r="H37" s="3">
+      <c r="J37" s="3">
         <v>219</v>
       </c>
-      <c r="I37" s="3">
+      <c r="K37" s="3">
         <v>450</v>
       </c>
-      <c r="J37" s="3">
+      <c r="L37" s="3">
         <v>91</v>
       </c>
-      <c r="K37" s="3">
+      <c r="M37" s="3">
         <v>113</v>
       </c>
-      <c r="L37" s="3">
+      <c r="N37" s="3">
         <v>1</v>
       </c>
-      <c r="M37" s="3">
+      <c r="O37" s="3">
         <v>3</v>
       </c>
-      <c r="N37" s="3">
+      <c r="P37" s="3">
         <v>2</v>
       </c>
-      <c r="O37" s="3">
+      <c r="Q37" s="3">
         <v>9</v>
       </c>
-      <c r="P37" s="8">
+      <c r="R37" s="8">
         <f t="shared" si="1"/>
         <v>4.1095890410958908</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A38" s="3">
-        <v>11</v>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A38" s="4">
+        <v>11037</v>
       </c>
       <c r="B38" s="3">
+        <v>11</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D38" s="3">
         <v>37</v>
       </c>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3">
+      <c r="E38" s="3"/>
+      <c r="F38" s="3">
         <v>573</v>
       </c>
-      <c r="E38" s="3">
+      <c r="G38" s="3">
         <v>0</v>
       </c>
-      <c r="F38" s="3">
+      <c r="H38" s="3">
         <v>110</v>
       </c>
-      <c r="G38" s="3">
+      <c r="I38" s="3">
         <v>256</v>
       </c>
-      <c r="H38" s="3">
+      <c r="J38" s="3">
         <v>290</v>
       </c>
-      <c r="I38" s="3">
+      <c r="K38" s="3">
         <v>500</v>
       </c>
-      <c r="J38" s="3">
+      <c r="L38" s="3">
         <v>133</v>
       </c>
-      <c r="K38" s="3">
+      <c r="M38" s="3">
         <v>135</v>
       </c>
-      <c r="L38" s="3">
+      <c r="N38" s="3">
         <v>1</v>
       </c>
-      <c r="M38" s="3">
+      <c r="O38" s="3">
         <v>5</v>
       </c>
-      <c r="N38" s="3">
+      <c r="P38" s="3">
         <v>6</v>
       </c>
-      <c r="O38" s="3">
+      <c r="Q38" s="3">
         <v>10</v>
       </c>
-      <c r="P38" s="8">
+      <c r="R38" s="8">
         <f t="shared" si="1"/>
         <v>3.4482758620689653</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A39" s="3">
-        <v>11</v>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A39" s="4">
+        <v>11038</v>
       </c>
       <c r="B39" s="3">
+        <v>11</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D39" s="3">
         <v>38</v>
       </c>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3">
+      <c r="E39" s="3"/>
+      <c r="F39" s="3">
         <v>1080</v>
       </c>
-      <c r="E39" s="3">
+      <c r="G39" s="3">
         <v>6</v>
       </c>
-      <c r="F39" s="3">
+      <c r="H39" s="3">
         <v>133</v>
       </c>
-      <c r="G39" s="3">
+      <c r="I39" s="3">
         <v>234</v>
       </c>
-      <c r="H39" s="3">
+      <c r="J39" s="3">
         <v>245</v>
       </c>
-      <c r="I39" s="3">
+      <c r="K39" s="3">
         <v>800</v>
       </c>
-      <c r="J39" s="3">
+      <c r="L39" s="3">
         <v>53</v>
       </c>
-      <c r="K39" s="3">
+      <c r="M39" s="3">
         <v>177</v>
       </c>
-      <c r="L39" s="3">
+      <c r="N39" s="3">
         <v>1</v>
       </c>
-      <c r="M39" s="3">
+      <c r="O39" s="3">
         <v>2</v>
       </c>
-      <c r="N39" s="3">
+      <c r="P39" s="3">
         <v>4</v>
       </c>
-      <c r="O39" s="3">
+      <c r="Q39" s="3">
         <v>8</v>
       </c>
-      <c r="P39" s="8">
+      <c r="R39" s="8">
         <f t="shared" si="1"/>
         <v>3.2653061224489797</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A40" s="3">
-        <v>11</v>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A40" s="4">
+        <v>11039</v>
       </c>
       <c r="B40" s="3">
+        <v>11</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D40" s="3">
         <v>39</v>
       </c>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3">
+      <c r="E40" s="3"/>
+      <c r="F40" s="3">
         <v>1240</v>
       </c>
-      <c r="E40" s="3">
+      <c r="G40" s="3">
         <v>6</v>
       </c>
-      <c r="F40" s="3">
+      <c r="H40" s="3">
         <v>167</v>
       </c>
-      <c r="G40" s="3">
+      <c r="I40" s="3">
         <v>282</v>
       </c>
-      <c r="H40" s="3">
+      <c r="J40" s="3">
         <v>338</v>
       </c>
-      <c r="I40" s="3">
+      <c r="K40" s="3">
         <v>1000</v>
       </c>
-      <c r="J40" s="3">
+      <c r="L40" s="3">
         <v>52</v>
       </c>
-      <c r="K40" s="3">
+      <c r="M40" s="3">
         <v>250</v>
       </c>
-      <c r="L40" s="3">
+      <c r="N40" s="3">
         <v>2</v>
       </c>
-      <c r="M40" s="3">
+      <c r="O40" s="3">
         <v>9</v>
       </c>
-      <c r="N40" s="3">
+      <c r="P40" s="3">
         <v>1</v>
       </c>
-      <c r="O40" s="3">
+      <c r="Q40" s="3">
         <v>12</v>
       </c>
-      <c r="P40" s="8">
+      <c r="R40" s="8">
         <f t="shared" si="1"/>
         <v>3.5502958579881656</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A41" s="3">
-        <v>11</v>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A41" s="4">
+        <v>11040</v>
       </c>
       <c r="B41" s="3">
+        <v>11</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D41" s="3">
         <v>40</v>
       </c>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3">
+      <c r="E41" s="3"/>
+      <c r="F41" s="3">
         <v>891</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>7</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>81</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>149</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>186</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>21</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>147</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>3</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>13</v>
       </c>
-      <c r="P41" s="8">
+      <c r="R41" s="8">
         <f t="shared" si="1"/>
         <v>6.989247311827957</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A42" s="3">
-        <v>11</v>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A42" s="4">
+        <v>11041</v>
       </c>
       <c r="B42" s="3">
+        <v>11</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D42" s="3">
         <v>41</v>
       </c>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3">
+      <c r="E42" s="3"/>
+      <c r="F42" s="3">
         <v>988</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>6</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>101</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>179</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>850</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>27</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>154</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>1</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>7</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="O42" s="3">
-        <v>11</v>
-      </c>
-      <c r="P42" s="8">
+      <c r="Q42" s="3">
+        <v>11</v>
+      </c>
+      <c r="R42" s="8">
         <f t="shared" si="1"/>
         <v>5.5</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A43" s="3">
-        <v>11</v>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A43" s="4">
+        <v>11042</v>
       </c>
       <c r="B43" s="3">
+        <v>11</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D43" s="3">
         <v>42</v>
       </c>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3">
+      <c r="E43" s="3"/>
+      <c r="F43" s="3">
         <v>1425</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>3</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>159</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>270</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>304</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>25</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>256</v>
-      </c>
-      <c r="L43" s="3">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3">
-        <v>7</v>
       </c>
       <c r="N43" s="3">
         <v>3</v>
       </c>
       <c r="O43" s="3">
+        <v>7</v>
+      </c>
+      <c r="P43" s="3">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3">
         <v>10</v>
       </c>
-      <c r="P43" s="8">
+      <c r="R43" s="8">
         <f t="shared" si="1"/>
         <v>3.2894736842105261</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A44" s="3">
-        <v>11</v>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A44" s="4">
+        <v>11043</v>
       </c>
       <c r="B44" s="3">
+        <v>11</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D44" s="3">
         <v>43</v>
       </c>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3">
+      <c r="E44" s="3"/>
+      <c r="F44" s="3">
         <v>1104</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>9</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>96</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>163</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>167</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>37</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>114</v>
-      </c>
-      <c r="L44" s="3">
-        <v>2</v>
-      </c>
-      <c r="M44" s="3">
-        <v>2</v>
       </c>
       <c r="N44" s="3">
         <v>2</v>
       </c>
       <c r="O44" s="3">
+        <v>2</v>
+      </c>
+      <c r="P44" s="3">
+        <v>2</v>
+      </c>
+      <c r="Q44" s="3">
         <v>10</v>
       </c>
-      <c r="P44" s="8">
+      <c r="R44" s="8">
         <f t="shared" si="1"/>
         <v>5.9880239520958085</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A45" s="3">
-        <v>11</v>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A45" s="4">
+        <v>11044</v>
       </c>
       <c r="B45" s="3">
+        <v>11</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D45" s="3">
         <v>44</v>
       </c>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3">
+      <c r="E45" s="3"/>
+      <c r="F45" s="3">
         <v>1641</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>6</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>161</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>293</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>335</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>40</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>270</v>
-      </c>
-      <c r="L45" s="3">
-        <v>2</v>
-      </c>
-      <c r="M45" s="3">
-        <v>8</v>
       </c>
       <c r="N45" s="3">
         <v>2</v>
       </c>
       <c r="O45" s="3">
+        <v>8</v>
+      </c>
+      <c r="P45" s="3">
+        <v>2</v>
+      </c>
+      <c r="Q45" s="3">
         <v>13</v>
       </c>
-      <c r="P45" s="8">
+      <c r="R45" s="8">
         <f t="shared" si="1"/>
         <v>3.8805970149253732</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A46" s="3">
-        <v>11</v>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A46" s="4">
+        <v>11045</v>
       </c>
       <c r="B46" s="3">
+        <v>11</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" s="3">
         <v>45</v>
       </c>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3">
+      <c r="E46" s="3"/>
+      <c r="F46" s="3">
         <v>1701</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>8</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>129</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>233</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>262</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>61</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>187</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>0</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>4</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>9</v>
       </c>
-      <c r="P46" s="8">
+      <c r="R46" s="8">
         <f t="shared" si="1"/>
         <v>3.4351145038167941</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A47" s="3">
-        <v>11</v>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A47" s="4">
+        <v>11046</v>
       </c>
       <c r="B47" s="3">
+        <v>11</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D47" s="3">
         <v>46</v>
       </c>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3">
+      <c r="E47" s="3"/>
+      <c r="F47" s="3">
         <v>1537</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>7</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>104</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>219</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>236</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>1400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>41</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>165</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>5</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>4</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>6</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>15</v>
       </c>
-      <c r="P47" s="8">
+      <c r="R47" s="8">
         <f t="shared" si="1"/>
         <v>6.3559322033898304</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A48" s="3">
-        <v>11</v>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A48" s="4">
+        <v>11047</v>
       </c>
       <c r="B48" s="3">
+        <v>11</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D48" s="3">
         <v>47</v>
       </c>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3">
+      <c r="E48" s="3"/>
+      <c r="F48" s="3">
         <v>1383</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>7</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>136</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>251</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>287</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>48</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>219</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>3</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>5</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>4</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>9</v>
       </c>
-      <c r="P48" s="8">
+      <c r="R48" s="8">
         <f t="shared" si="1"/>
         <v>3.1358885017421603</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A49" s="3">
-        <v>11</v>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A49" s="4">
+        <v>11048</v>
       </c>
       <c r="B49" s="3">
+        <v>11</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D49" s="3">
         <v>48</v>
       </c>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3">
+      <c r="E49" s="3"/>
+      <c r="F49" s="3">
         <v>1346</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>8</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>153</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>251</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>289</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>45</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>208</v>
-      </c>
-      <c r="L49" s="3">
-        <v>3</v>
-      </c>
-      <c r="M49" s="3">
-        <v>6</v>
       </c>
       <c r="N49" s="3">
         <v>3</v>
       </c>
       <c r="O49" s="3">
+        <v>6</v>
+      </c>
+      <c r="P49" s="3">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3">
         <v>22</v>
       </c>
-      <c r="P49" s="8">
+      <c r="R49" s="8">
         <f t="shared" si="1"/>
         <v>7.6124567474048446</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A50" s="3">
-        <v>11</v>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A50" s="4">
+        <v>11049</v>
       </c>
       <c r="B50" s="3">
+        <v>11</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D50" s="3">
         <v>49</v>
       </c>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3">
+      <c r="E50" s="3"/>
+      <c r="F50" s="3">
         <v>730</v>
       </c>
-      <c r="E50" s="3">
+      <c r="G50" s="3">
         <v>4</v>
       </c>
-      <c r="F50" s="3">
+      <c r="H50" s="3">
         <v>93</v>
       </c>
-      <c r="G50" s="3">
+      <c r="I50" s="3">
         <v>173</v>
       </c>
-      <c r="H50" s="3">
+      <c r="J50" s="3">
         <v>197</v>
       </c>
-      <c r="I50" s="3">
+      <c r="K50" s="3">
         <v>700</v>
       </c>
-      <c r="J50" s="3">
+      <c r="L50" s="3">
         <v>64</v>
       </c>
-      <c r="K50" s="3">
+      <c r="M50" s="3">
         <v>114</v>
-      </c>
-      <c r="L50" s="3">
-        <v>1</v>
-      </c>
-      <c r="M50" s="3">
-        <v>7</v>
       </c>
       <c r="N50" s="3">
         <v>1</v>
       </c>
       <c r="O50" s="3">
+        <v>7</v>
+      </c>
+      <c r="P50" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q50" s="3">
         <v>10</v>
       </c>
-      <c r="P50" s="8">
+      <c r="R50" s="8">
         <f t="shared" si="1"/>
         <v>5.0761421319796955</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A51" s="1">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A51" s="4">
+        <v>65001</v>
+      </c>
+      <c r="B51" s="1">
         <v>65</v>
       </c>
-      <c r="B51" s="1">
+      <c r="C51" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D51" s="1">
         <v>1</v>
       </c>
-      <c r="D51" s="1">
+      <c r="F51" s="1">
         <v>1136</v>
       </c>
-      <c r="E51" s="1">
+      <c r="G51" s="1">
         <v>7</v>
       </c>
-      <c r="F51" s="1">
+      <c r="H51" s="1">
         <v>164</v>
       </c>
-      <c r="G51" s="1">
+      <c r="I51" s="1">
         <v>394</v>
       </c>
-      <c r="H51" s="1">
+      <c r="J51" s="1">
         <v>488</v>
       </c>
-      <c r="I51" s="1">
+      <c r="K51" s="1">
         <v>1100</v>
       </c>
-      <c r="J51" s="1">
+      <c r="L51" s="1">
         <v>285</v>
       </c>
-      <c r="K51" s="1">
+      <c r="M51" s="1">
         <v>194</v>
       </c>
-      <c r="O51" s="1">
+      <c r="Q51" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A52" s="1">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A52" s="4">
+        <v>65002</v>
+      </c>
+      <c r="B52" s="1">
         <v>65</v>
       </c>
-      <c r="B52" s="1">
+      <c r="C52" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D52" s="1">
         <v>2</v>
       </c>
-      <c r="D52" s="1">
+      <c r="F52" s="1">
         <v>1219</v>
       </c>
-      <c r="E52" s="1">
+      <c r="G52" s="1">
         <v>4</v>
       </c>
-      <c r="F52" s="1">
+      <c r="H52" s="1">
         <v>135</v>
       </c>
-      <c r="G52" s="1">
+      <c r="I52" s="1">
         <v>352</v>
       </c>
-      <c r="H52" s="1">
+      <c r="J52" s="1">
         <v>445</v>
       </c>
-      <c r="I52" s="1">
+      <c r="K52" s="1">
         <v>1150</v>
       </c>
-      <c r="J52" s="1">
+      <c r="L52" s="1">
         <v>139</v>
       </c>
-      <c r="K52" s="1">
+      <c r="M52" s="1">
         <v>289</v>
       </c>
-      <c r="O52" s="1">
+      <c r="Q52" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A53" s="1">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A53" s="4">
+        <v>65003</v>
+      </c>
+      <c r="B53" s="1">
         <v>65</v>
       </c>
-      <c r="B53" s="1">
+      <c r="C53" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D53" s="1">
         <v>3</v>
       </c>
-      <c r="D53" s="1">
+      <c r="F53" s="1">
         <v>472</v>
       </c>
-      <c r="E53" s="1">
+      <c r="G53" s="1">
         <v>5</v>
       </c>
-      <c r="F53" s="1">
+      <c r="H53" s="1">
         <v>89</v>
       </c>
-      <c r="G53" s="1">
+      <c r="I53" s="1">
         <v>192</v>
       </c>
-      <c r="H53" s="1">
+      <c r="J53" s="1">
         <v>228</v>
       </c>
-      <c r="I53" s="1">
+      <c r="K53" s="1">
         <v>500</v>
       </c>
-      <c r="J53" s="1">
+      <c r="L53" s="1">
         <v>63</v>
       </c>
-      <c r="K53" s="1">
+      <c r="M53" s="1">
         <v>160</v>
       </c>
-      <c r="O53" s="1">
+      <c r="Q53" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A54" s="1">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A54" s="4">
+        <v>65004</v>
+      </c>
+      <c r="B54" s="1">
         <v>65</v>
       </c>
-      <c r="B54" s="1">
+      <c r="C54" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D54" s="1">
         <v>4</v>
       </c>
-      <c r="D54" s="1">
+      <c r="F54" s="1">
         <v>1041</v>
       </c>
-      <c r="E54" s="1">
+      <c r="G54" s="1">
         <v>1</v>
       </c>
-      <c r="F54" s="1">
+      <c r="H54" s="1">
         <v>141</v>
       </c>
-      <c r="G54" s="1">
+      <c r="I54" s="1">
         <v>366</v>
       </c>
-      <c r="H54" s="1">
+      <c r="J54" s="1">
         <v>413</v>
       </c>
-      <c r="I54" s="1">
+      <c r="K54" s="1">
         <v>1000</v>
       </c>
-      <c r="J54" s="1">
+      <c r="L54" s="1">
         <v>162</v>
       </c>
-      <c r="K54" s="1">
+      <c r="M54" s="1">
         <v>233</v>
       </c>
-      <c r="O54" s="1">
+      <c r="Q54" s="1">
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A55" s="1">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A55" s="4">
+        <v>65005</v>
+      </c>
+      <c r="B55" s="1">
         <v>65</v>
       </c>
-      <c r="B55" s="1">
+      <c r="C55" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D55" s="1">
         <v>5</v>
       </c>
-      <c r="D55" s="1">
+      <c r="F55" s="1">
         <v>538</v>
       </c>
-      <c r="E55" s="1">
+      <c r="G55" s="1">
         <v>2</v>
       </c>
-      <c r="F55" s="1">
+      <c r="H55" s="1">
         <v>71</v>
       </c>
-      <c r="G55" s="1">
+      <c r="I55" s="1">
         <v>179</v>
       </c>
-      <c r="H55" s="1">
+      <c r="J55" s="1">
         <v>221</v>
       </c>
-      <c r="I55" s="1">
+      <c r="K55" s="1">
         <v>500</v>
       </c>
-      <c r="J55" s="1">
+      <c r="L55" s="1">
         <v>77</v>
       </c>
-      <c r="K55" s="1">
+      <c r="M55" s="1">
         <v>131</v>
       </c>
-      <c r="O55" s="1">
+      <c r="Q55" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A56" s="1">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A56" s="4">
+        <v>65006</v>
+      </c>
+      <c r="B56" s="1">
         <v>65</v>
       </c>
-      <c r="B56" s="1">
+      <c r="C56" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D56" s="1">
         <v>6</v>
       </c>
-      <c r="D56" s="1">
+      <c r="F56" s="1">
         <v>503</v>
       </c>
-      <c r="E56" s="1">
+      <c r="G56" s="1">
         <v>7</v>
       </c>
-      <c r="F56" s="1">
+      <c r="H56" s="1">
         <v>70</v>
       </c>
-      <c r="G56" s="1">
+      <c r="I56" s="1">
         <v>157</v>
       </c>
-      <c r="H56" s="1">
+      <c r="J56" s="1">
         <v>235</v>
       </c>
-      <c r="I56" s="1">
+      <c r="K56" s="1">
         <v>500</v>
       </c>
-      <c r="J56" s="1">
+      <c r="L56" s="1">
         <v>128</v>
       </c>
-      <c r="K56" s="1">
+      <c r="M56" s="1">
         <v>102</v>
       </c>
-      <c r="O56" s="1">
+      <c r="Q56" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A57" s="1">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A57" s="4">
+        <v>65007</v>
+      </c>
+      <c r="B57" s="1">
         <v>65</v>
       </c>
-      <c r="B57" s="1">
+      <c r="C57" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D57" s="1">
         <v>7</v>
       </c>
-      <c r="D57" s="1">
+      <c r="F57" s="1">
         <v>712</v>
       </c>
-      <c r="E57" s="1">
+      <c r="G57" s="1">
         <v>2</v>
       </c>
-      <c r="F57" s="1">
+      <c r="H57" s="1">
         <v>91</v>
       </c>
-      <c r="G57" s="1">
+      <c r="I57" s="1">
         <v>229</v>
       </c>
-      <c r="H57" s="1">
+      <c r="J57" s="1">
         <v>271</v>
       </c>
-      <c r="I57" s="1">
+      <c r="K57" s="1">
         <v>650</v>
       </c>
-      <c r="J57" s="1">
+      <c r="L57" s="1">
         <v>134</v>
       </c>
-      <c r="K57" s="1">
+      <c r="M57" s="1">
         <v>129</v>
       </c>
-      <c r="O57" s="1">
+      <c r="Q57" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A58" s="1">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A58" s="4">
+        <v>65008</v>
+      </c>
+      <c r="B58" s="1">
         <v>65</v>
       </c>
-      <c r="B58" s="1">
+      <c r="C58" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D58" s="1">
         <v>8</v>
       </c>
-      <c r="D58" s="1">
+      <c r="F58" s="1">
         <v>590</v>
       </c>
-      <c r="E58" s="1">
+      <c r="G58" s="1">
         <v>3</v>
       </c>
-      <c r="F58" s="1">
+      <c r="H58" s="1">
         <v>105</v>
       </c>
-      <c r="G58" s="1">
+      <c r="I58" s="1">
         <v>215</v>
       </c>
-      <c r="H58" s="1">
+      <c r="J58" s="1">
         <v>250</v>
       </c>
-      <c r="I58" s="1">
+      <c r="K58" s="1">
         <v>550</v>
       </c>
-      <c r="J58" s="1">
+      <c r="L58" s="1">
         <v>50</v>
       </c>
-      <c r="K58" s="1">
+      <c r="M58" s="1">
         <v>194</v>
       </c>
-      <c r="O58" s="1">
+      <c r="Q58" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A59" s="1">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A59" s="4">
+        <v>65009</v>
+      </c>
+      <c r="B59" s="1">
         <v>65</v>
       </c>
-      <c r="B59" s="1">
+      <c r="C59" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D59" s="1">
         <v>9</v>
       </c>
-      <c r="D59" s="1">
+      <c r="F59" s="1">
         <v>1065</v>
       </c>
-      <c r="E59" s="1">
+      <c r="G59" s="1">
         <v>4</v>
       </c>
-      <c r="F59" s="1">
+      <c r="H59" s="1">
         <v>148</v>
       </c>
-      <c r="G59" s="1">
+      <c r="I59" s="1">
         <v>365</v>
       </c>
-      <c r="H59" s="1">
+      <c r="J59" s="1">
         <v>450</v>
       </c>
-      <c r="I59" s="1">
+      <c r="K59" s="1">
         <v>1000</v>
       </c>
-      <c r="J59" s="1">
+      <c r="L59" s="1">
         <v>96</v>
       </c>
-      <c r="K59" s="1">
+      <c r="M59" s="1">
         <v>334</v>
       </c>
-      <c r="O59" s="1">
+      <c r="Q59" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A60" s="1">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A60" s="4">
+        <v>65010</v>
+      </c>
+      <c r="B60" s="1">
         <v>65</v>
       </c>
-      <c r="B60" s="1">
+      <c r="C60" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D60" s="1">
         <v>10</v>
       </c>
-      <c r="D60" s="1">
+      <c r="F60" s="1">
         <v>926</v>
       </c>
-      <c r="E60" s="1">
+      <c r="G60" s="1">
         <v>3</v>
       </c>
-      <c r="F60" s="1">
+      <c r="H60" s="1">
         <v>131</v>
       </c>
-      <c r="G60" s="1">
+      <c r="I60" s="1">
         <v>314</v>
       </c>
-      <c r="H60" s="1">
+      <c r="J60" s="1">
         <v>400</v>
       </c>
-      <c r="I60" s="1">
+      <c r="K60" s="1">
         <v>900</v>
       </c>
-      <c r="J60" s="1">
+      <c r="L60" s="1">
         <v>103</v>
       </c>
-      <c r="K60" s="1">
+      <c r="M60" s="1">
         <v>277</v>
       </c>
-      <c r="O60" s="1">
+      <c r="Q60" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A61" s="1">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A61" s="4">
+        <v>65011</v>
+      </c>
+      <c r="B61" s="1">
         <v>65</v>
       </c>
-      <c r="B61" s="1">
-        <v>11</v>
+      <c r="C61" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="D61" s="1">
+        <v>11</v>
+      </c>
+      <c r="F61" s="1">
         <v>722</v>
       </c>
-      <c r="E61" s="1">
+      <c r="G61" s="1">
         <v>1</v>
       </c>
-      <c r="F61" s="1">
+      <c r="H61" s="1">
         <v>166</v>
       </c>
-      <c r="G61" s="1">
+      <c r="I61" s="1">
         <v>362</v>
       </c>
-      <c r="H61" s="1">
+      <c r="J61" s="1">
         <v>404</v>
       </c>
-      <c r="I61" s="1">
+      <c r="K61" s="1">
         <v>700</v>
       </c>
-      <c r="J61" s="1">
+      <c r="L61" s="1">
         <v>46</v>
       </c>
-      <c r="K61" s="1">
+      <c r="M61" s="1">
         <v>352</v>
       </c>
-      <c r="O61" s="1">
+      <c r="Q61" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A62" s="1">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A62" s="4">
+        <v>65012</v>
+      </c>
+      <c r="B62" s="1">
         <v>65</v>
       </c>
-      <c r="B62" s="1">
+      <c r="C62" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D62" s="1">
         <v>12</v>
       </c>
-      <c r="D62" s="1">
+      <c r="F62" s="1">
         <v>765</v>
       </c>
-      <c r="E62" s="1">
+      <c r="G62" s="1">
         <v>3</v>
       </c>
-      <c r="F62" s="1">
+      <c r="H62" s="1">
         <v>117</v>
       </c>
-      <c r="G62" s="1">
+      <c r="I62" s="1">
         <v>306</v>
       </c>
-      <c r="H62" s="1">
+      <c r="J62" s="1">
         <v>353</v>
       </c>
-      <c r="I62" s="1">
+      <c r="K62" s="1">
         <v>750</v>
       </c>
-      <c r="J62" s="1">
+      <c r="L62" s="1">
         <v>125</v>
       </c>
-      <c r="K62" s="1">
+      <c r="M62" s="1">
         <v>206</v>
       </c>
-      <c r="O62" s="1">
+      <c r="Q62" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A63" s="1">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A63" s="4">
+        <v>65013</v>
+      </c>
+      <c r="B63" s="1">
         <v>65</v>
       </c>
-      <c r="B63" s="1">
+      <c r="C63" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D63" s="1">
         <v>13</v>
       </c>
-      <c r="D63" s="1">
+      <c r="F63" s="1">
         <v>1346</v>
       </c>
-      <c r="E63" s="1">
+      <c r="G63" s="1">
         <v>2</v>
       </c>
-      <c r="F63" s="1">
+      <c r="H63" s="1">
         <v>123</v>
       </c>
-      <c r="G63" s="1">
+      <c r="I63" s="1">
         <v>384</v>
       </c>
-      <c r="H63" s="1">
+      <c r="J63" s="1">
         <v>486</v>
       </c>
-      <c r="I63" s="1">
+      <c r="K63" s="1">
         <v>1300</v>
       </c>
-      <c r="J63" s="1">
+      <c r="L63" s="1">
         <v>94</v>
       </c>
-      <c r="K63" s="1">
+      <c r="M63" s="1">
         <v>374</v>
       </c>
-      <c r="O63" s="1">
+      <c r="Q63" s="1">
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.5">
-      <c r="A64" s="1">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.5">
+      <c r="A64" s="4">
+        <v>65014</v>
+      </c>
+      <c r="B64" s="1">
         <v>65</v>
       </c>
-      <c r="B64" s="1">
+      <c r="C64" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D64" s="1">
         <v>14</v>
       </c>
-      <c r="D64" s="1">
+      <c r="F64" s="1">
         <v>828</v>
       </c>
-      <c r="E64" s="1">
+      <c r="G64" s="1">
         <v>2</v>
       </c>
-      <c r="F64" s="1">
+      <c r="H64" s="1">
         <v>112</v>
       </c>
-      <c r="G64" s="1">
+      <c r="I64" s="1">
         <v>324</v>
       </c>
-      <c r="H64" s="1">
+      <c r="J64" s="1">
         <v>369</v>
       </c>
-      <c r="I64" s="1">
+      <c r="K64" s="1">
         <v>750</v>
       </c>
-      <c r="J64" s="1">
+      <c r="L64" s="1">
         <v>53</v>
       </c>
-      <c r="K64" s="1">
+      <c r="M64" s="1">
         <v>309</v>
       </c>
-      <c r="O64" s="1">
+      <c r="Q64" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="A65" s="1">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="A65" s="4">
+        <v>65015</v>
+      </c>
+      <c r="B65" s="1">
         <v>65</v>
       </c>
-      <c r="B65" s="1">
+      <c r="C65" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D65" s="1">
         <v>15</v>
       </c>
-      <c r="D65" s="1">
+      <c r="F65" s="1">
         <v>586</v>
       </c>
-      <c r="E65" s="1">
+      <c r="G65" s="1">
         <v>3</v>
       </c>
-      <c r="F65" s="1">
+      <c r="H65" s="1">
         <v>126</v>
       </c>
-      <c r="G65" s="1">
+      <c r="I65" s="1">
         <v>242</v>
       </c>
-      <c r="H65" s="1">
+      <c r="J65" s="1">
         <v>275</v>
       </c>
-      <c r="I65" s="1">
+      <c r="K65" s="1">
         <v>550</v>
       </c>
-      <c r="J65" s="1">
+      <c r="L65" s="1">
         <v>117</v>
       </c>
-      <c r="K65" s="1">
+      <c r="M65" s="1">
         <v>133</v>
       </c>
-      <c r="O65" s="1">
+      <c r="Q65" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="A66" s="1">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="A66" s="4">
+        <v>65016</v>
+      </c>
+      <c r="B66" s="1">
         <v>65</v>
       </c>
-      <c r="B66" s="1">
+      <c r="C66" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D66" s="1">
         <v>16</v>
       </c>
-      <c r="D66" s="1">
+      <c r="F66" s="1">
         <v>378</v>
       </c>
-      <c r="E66" s="1">
+      <c r="G66" s="1">
         <v>0</v>
       </c>
-      <c r="F66" s="1">
+      <c r="H66" s="1">
         <v>45</v>
       </c>
-      <c r="G66" s="1">
+      <c r="I66" s="1">
         <v>141</v>
       </c>
-      <c r="H66" s="1">
+      <c r="J66" s="1">
         <v>178</v>
       </c>
-      <c r="I66" s="1">
+      <c r="K66" s="1">
         <v>400</v>
       </c>
-      <c r="J66" s="1">
+      <c r="L66" s="1">
         <v>102</v>
       </c>
-      <c r="K66" s="1">
+      <c r="M66" s="1">
         <v>74</v>
       </c>
-      <c r="O66" s="1">
+      <c r="Q66" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="A67" s="1">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="A67" s="4">
+        <v>65017</v>
+      </c>
+      <c r="B67" s="1">
         <v>65</v>
       </c>
-      <c r="B67" s="1">
+      <c r="C67" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D67" s="1">
         <v>17</v>
       </c>
-      <c r="D67" s="1">
+      <c r="F67" s="1">
         <v>807</v>
       </c>
-      <c r="E67" s="1">
+      <c r="G67" s="1">
         <v>2</v>
       </c>
-      <c r="F67" s="1">
+      <c r="H67" s="1">
         <v>85</v>
       </c>
-      <c r="G67" s="1">
+      <c r="I67" s="1">
         <v>211</v>
       </c>
-      <c r="H67" s="1">
+      <c r="J67" s="1">
         <v>282</v>
       </c>
-      <c r="I67" s="1">
+      <c r="K67" s="1">
         <v>750</v>
       </c>
-      <c r="J67" s="1">
+      <c r="L67" s="1">
         <v>55</v>
       </c>
-      <c r="K67" s="1">
+      <c r="M67" s="1">
         <v>211</v>
       </c>
-      <c r="O67" s="1">
+      <c r="Q67" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="A68" s="1">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="A68" s="4">
+        <v>65018</v>
+      </c>
+      <c r="B68" s="1">
         <v>65</v>
       </c>
-      <c r="B68" s="1">
+      <c r="C68" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D68" s="1">
         <v>18</v>
       </c>
-      <c r="D68" s="1">
+      <c r="F68" s="1">
         <v>938</v>
       </c>
-      <c r="E68" s="1">
+      <c r="G68" s="1">
         <v>2</v>
       </c>
-      <c r="F68" s="1">
+      <c r="H68" s="1">
         <v>120</v>
       </c>
-      <c r="G68" s="1">
+      <c r="I68" s="1">
         <v>326</v>
       </c>
-      <c r="H68" s="1">
+      <c r="J68" s="1">
         <v>386</v>
       </c>
-      <c r="I68" s="1">
+      <c r="K68" s="1">
         <v>900</v>
       </c>
-      <c r="J68" s="1">
+      <c r="L68" s="1">
         <v>118</v>
       </c>
-      <c r="K68" s="1">
+      <c r="M68" s="1">
         <v>256</v>
       </c>
-      <c r="O68" s="1">
+      <c r="Q68" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="A69" s="1">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="A69" s="4">
+        <v>65019</v>
+      </c>
+      <c r="B69" s="1">
         <v>65</v>
       </c>
-      <c r="B69" s="1">
+      <c r="C69" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D69" s="1">
         <v>19</v>
       </c>
-      <c r="D69" s="1">
+      <c r="F69" s="1">
         <v>897</v>
       </c>
-      <c r="E69" s="1">
+      <c r="G69" s="1">
         <v>4</v>
       </c>
-      <c r="F69" s="1">
+      <c r="H69" s="1">
         <v>62</v>
       </c>
-      <c r="G69" s="1">
+      <c r="I69" s="1">
         <v>223</v>
       </c>
-      <c r="H69" s="1">
+      <c r="J69" s="1">
         <v>321</v>
       </c>
-      <c r="I69" s="1">
+      <c r="K69" s="1">
         <v>850</v>
       </c>
-      <c r="J69" s="1">
+      <c r="L69" s="1">
         <v>97</v>
       </c>
-      <c r="K69" s="1">
+      <c r="M69" s="1">
         <v>205</v>
       </c>
-      <c r="O69" s="1">
+      <c r="Q69" s="1">
         <v>19</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="A70" s="1">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="A70" s="4">
+        <v>65020</v>
+      </c>
+      <c r="B70" s="1">
         <v>65</v>
       </c>
-      <c r="B70" s="1">
+      <c r="C70" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D70" s="1">
         <v>20</v>
       </c>
-      <c r="D70" s="1">
+      <c r="F70" s="1">
         <v>530</v>
       </c>
-      <c r="E70" s="1">
+      <c r="G70" s="1">
         <v>4</v>
       </c>
-      <c r="F70" s="1">
+      <c r="H70" s="1">
         <v>69</v>
       </c>
-      <c r="G70" s="1">
+      <c r="I70" s="1">
         <v>210</v>
       </c>
-      <c r="H70" s="1">
+      <c r="J70" s="1">
         <v>247</v>
       </c>
-      <c r="I70" s="1">
+      <c r="K70" s="1">
         <v>500</v>
       </c>
-      <c r="J70" s="1">
+      <c r="L70" s="1">
         <v>89</v>
       </c>
-      <c r="K70" s="1">
+      <c r="M70" s="1">
         <v>149</v>
       </c>
-      <c r="O70" s="1">
+      <c r="Q70" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="A71" s="1">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="A71" s="4">
+        <v>65021</v>
+      </c>
+      <c r="B71" s="1">
         <v>65</v>
       </c>
-      <c r="B71" s="1">
+      <c r="C71" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D71" s="1">
         <v>21</v>
       </c>
-      <c r="D71" s="1">
+      <c r="F71" s="1">
         <v>1266</v>
       </c>
-      <c r="E71" s="1">
+      <c r="G71" s="1">
         <v>1</v>
       </c>
-      <c r="F71" s="1">
+      <c r="H71" s="1">
         <v>175</v>
       </c>
-      <c r="G71" s="1">
+      <c r="I71" s="1">
         <v>448</v>
       </c>
-      <c r="H71" s="1">
+      <c r="J71" s="1">
         <v>546</v>
       </c>
-      <c r="I71" s="1">
+      <c r="K71" s="1">
         <v>1200</v>
       </c>
-      <c r="J71" s="1">
+      <c r="L71" s="1">
         <v>129</v>
       </c>
-      <c r="K71" s="1">
+      <c r="M71" s="1">
         <v>394</v>
       </c>
-      <c r="O71" s="1">
+      <c r="Q71" s="1">
         <v>23</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="A72" s="1">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="A72" s="4">
+        <v>65022</v>
+      </c>
+      <c r="B72" s="1">
         <v>65</v>
       </c>
-      <c r="B72" s="1">
+      <c r="C72" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D72" s="1">
         <v>22</v>
       </c>
-      <c r="D72" s="1">
+      <c r="F72" s="1">
         <v>628</v>
       </c>
-      <c r="E72" s="1">
+      <c r="G72" s="1">
         <v>2</v>
       </c>
-      <c r="F72" s="1">
+      <c r="H72" s="1">
         <v>111</v>
       </c>
-      <c r="G72" s="1">
+      <c r="I72" s="1">
         <v>250</v>
       </c>
-      <c r="H72" s="1">
+      <c r="J72" s="1">
         <v>292</v>
       </c>
-      <c r="I72" s="1">
+      <c r="K72" s="1">
         <v>600</v>
       </c>
-      <c r="J72" s="1">
+      <c r="L72" s="1">
         <v>87</v>
       </c>
-      <c r="K72" s="1">
+      <c r="M72" s="1">
         <v>196</v>
       </c>
-      <c r="O72" s="1">
+      <c r="Q72" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="A73" s="1">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="A73" s="4">
+        <v>65023</v>
+      </c>
+      <c r="B73" s="1">
         <v>65</v>
       </c>
-      <c r="B73" s="1">
+      <c r="C73" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D73" s="1">
         <v>23</v>
       </c>
-      <c r="D73" s="1">
+      <c r="F73" s="1">
         <v>497</v>
       </c>
-      <c r="E73" s="1">
+      <c r="G73" s="1">
         <v>1</v>
       </c>
-      <c r="F73" s="1">
+      <c r="H73" s="1">
         <v>77</v>
       </c>
-      <c r="G73" s="1">
+      <c r="I73" s="1">
         <v>185</v>
       </c>
-      <c r="H73" s="1">
+      <c r="J73" s="1">
         <v>242</v>
       </c>
-      <c r="I73" s="1">
+      <c r="K73" s="1">
         <v>500</v>
       </c>
-      <c r="J73" s="1">
+      <c r="L73" s="1">
         <v>56</v>
       </c>
-      <c r="K73" s="1">
+      <c r="M73" s="1">
         <v>180</v>
       </c>
-      <c r="O73" s="1">
+      <c r="Q73" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="A74" s="1">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="A74" s="4">
+        <v>65024</v>
+      </c>
+      <c r="B74" s="1">
         <v>65</v>
       </c>
-      <c r="B74" s="1">
+      <c r="C74" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D74" s="1">
         <v>24</v>
       </c>
-      <c r="D74" s="1">
+      <c r="F74" s="1">
         <v>253</v>
       </c>
-      <c r="E74" s="1">
+      <c r="G74" s="1">
         <v>4</v>
       </c>
-      <c r="F74" s="1">
+      <c r="H74" s="1">
         <v>59</v>
       </c>
-      <c r="G74" s="1">
+      <c r="I74" s="1">
         <v>75</v>
       </c>
-      <c r="H74" s="1">
+      <c r="J74" s="1">
         <v>143</v>
       </c>
-      <c r="I74" s="1">
+      <c r="K74" s="1">
         <v>250</v>
       </c>
-      <c r="J74" s="1">
+      <c r="L74" s="1">
         <v>58</v>
       </c>
-      <c r="K74" s="1">
+      <c r="M74" s="1">
         <v>85</v>
       </c>
-      <c r="O74" s="1">
+      <c r="Q74" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="A75" s="1">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="A75" s="4">
+        <v>65025</v>
+      </c>
+      <c r="B75" s="1">
         <v>65</v>
       </c>
-      <c r="B75" s="1">
+      <c r="C75" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D75" s="1">
         <v>25</v>
       </c>
-      <c r="D75" s="1">
+      <c r="F75" s="1">
         <v>1073</v>
       </c>
-      <c r="E75" s="1">
+      <c r="G75" s="1">
         <v>0</v>
       </c>
-      <c r="F75" s="1">
+      <c r="H75" s="1">
         <v>112</v>
       </c>
-      <c r="G75" s="1">
+      <c r="I75" s="1">
         <v>292</v>
       </c>
-      <c r="H75" s="1">
+      <c r="J75" s="1">
         <v>420</v>
       </c>
-      <c r="I75" s="1">
+      <c r="K75" s="1">
         <v>1050</v>
       </c>
-      <c r="J75" s="1">
+      <c r="L75" s="1">
         <v>57</v>
       </c>
-      <c r="K75" s="1">
+      <c r="M75" s="1">
         <v>353</v>
       </c>
-      <c r="O75" s="1">
+      <c r="Q75" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="A76" s="1">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="A76" s="4">
+        <v>65026</v>
+      </c>
+      <c r="B76" s="1">
         <v>65</v>
       </c>
-      <c r="B76" s="1">
+      <c r="C76" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D76" s="1">
         <v>26</v>
       </c>
-      <c r="D76" s="1">
+      <c r="F76" s="1">
         <v>1117</v>
       </c>
-      <c r="E76" s="1">
+      <c r="G76" s="1">
         <v>2</v>
       </c>
-      <c r="F76" s="1">
+      <c r="H76" s="1">
         <v>157</v>
       </c>
-      <c r="G76" s="1">
+      <c r="I76" s="1">
         <v>389</v>
       </c>
-      <c r="H76" s="1">
+      <c r="J76" s="1">
         <v>474</v>
       </c>
-      <c r="I76" s="1">
+      <c r="K76" s="1">
         <v>1050</v>
       </c>
-      <c r="J76" s="1">
+      <c r="L76" s="1">
         <v>90</v>
       </c>
-      <c r="K76" s="1">
+      <c r="M76" s="1">
         <v>368</v>
       </c>
-      <c r="O76" s="1">
+      <c r="Q76" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="A77" s="1">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="A77" s="4">
+        <v>65027</v>
+      </c>
+      <c r="B77" s="1">
         <v>65</v>
       </c>
-      <c r="B77" s="1">
+      <c r="C77" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D77" s="1">
         <v>27</v>
       </c>
-      <c r="D77" s="1">
+      <c r="F77" s="1">
         <v>986</v>
       </c>
-      <c r="E77" s="1">
+      <c r="G77" s="1">
         <v>4</v>
       </c>
-      <c r="F77" s="1">
+      <c r="H77" s="1">
         <v>121</v>
       </c>
-      <c r="G77" s="1">
+      <c r="I77" s="1">
         <v>292</v>
       </c>
-      <c r="H77" s="1">
+      <c r="J77" s="1">
         <v>381</v>
       </c>
-      <c r="I77" s="1">
+      <c r="K77" s="1">
         <v>950</v>
       </c>
-      <c r="J77" s="1">
+      <c r="L77" s="1">
         <v>80</v>
       </c>
-      <c r="K77" s="1">
+      <c r="M77" s="1">
         <v>294</v>
       </c>
-      <c r="O77" s="1">
+      <c r="Q77" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="A78" s="1">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="A78" s="4">
+        <v>65028</v>
+      </c>
+      <c r="B78" s="1">
         <v>65</v>
       </c>
-      <c r="B78" s="1">
+      <c r="C78" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D78" s="1">
         <v>28</v>
       </c>
-      <c r="D78" s="1">
+      <c r="F78" s="1">
         <v>808</v>
       </c>
-      <c r="E78" s="1">
+      <c r="G78" s="1">
         <v>2</v>
       </c>
-      <c r="F78" s="1">
+      <c r="H78" s="1">
         <v>108</v>
       </c>
-      <c r="G78" s="1">
+      <c r="I78" s="1">
         <v>320</v>
       </c>
-      <c r="H78" s="1">
+      <c r="J78" s="1">
         <v>376</v>
       </c>
-      <c r="I78" s="1">
+      <c r="K78" s="1">
         <v>750</v>
       </c>
-      <c r="J78" s="1">
+      <c r="L78" s="1">
         <v>165</v>
       </c>
-      <c r="K78" s="1">
+      <c r="M78" s="1">
         <v>201</v>
       </c>
-      <c r="O78" s="1">
+      <c r="Q78" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="A79" s="1">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="A79" s="4">
+        <v>65029</v>
+      </c>
+      <c r="B79" s="1">
         <v>65</v>
       </c>
-      <c r="B79" s="1">
+      <c r="C79" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D79" s="1">
         <v>29</v>
       </c>
-      <c r="D79" s="1">
+      <c r="F79" s="1">
         <v>777</v>
       </c>
-      <c r="E79" s="1">
+      <c r="G79" s="1">
         <v>1</v>
       </c>
-      <c r="F79" s="1">
+      <c r="H79" s="1">
         <v>90</v>
       </c>
-      <c r="G79" s="1">
+      <c r="I79" s="1">
         <v>250</v>
       </c>
-      <c r="H79" s="1">
+      <c r="J79" s="1">
         <v>309</v>
       </c>
-      <c r="I79" s="1">
+      <c r="K79" s="1">
         <v>750</v>
       </c>
-      <c r="J79" s="1">
+      <c r="L79" s="1">
         <v>93</v>
       </c>
-      <c r="K79" s="1">
+      <c r="M79" s="1">
         <v>204</v>
       </c>
-      <c r="O79" s="1">
+      <c r="Q79" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="A80" s="1">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="A80" s="4">
+        <v>65030</v>
+      </c>
+      <c r="B80" s="1">
         <v>65</v>
       </c>
-      <c r="B80" s="1">
+      <c r="C80" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D80" s="1">
         <v>30</v>
       </c>
-      <c r="D80" s="1">
+      <c r="F80" s="1">
         <v>1204</v>
       </c>
-      <c r="E80" s="1">
+      <c r="G80" s="1">
         <v>2</v>
       </c>
-      <c r="F80" s="1">
+      <c r="H80" s="1">
         <v>180</v>
       </c>
-      <c r="G80" s="1">
+      <c r="I80" s="1">
         <v>443</v>
       </c>
-      <c r="H80" s="1">
+      <c r="J80" s="1">
         <v>558</v>
       </c>
-      <c r="I80" s="1">
+      <c r="K80" s="1">
         <v>1150</v>
       </c>
-      <c r="J80" s="1">
+      <c r="L80" s="1">
         <v>53</v>
       </c>
-      <c r="K80" s="1">
+      <c r="M80" s="1">
         <v>487</v>
       </c>
-      <c r="O80" s="1">
+      <c r="Q80" s="1">
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="A81" s="1">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="A81" s="4">
+        <v>65031</v>
+      </c>
+      <c r="B81" s="1">
         <v>65</v>
       </c>
-      <c r="B81" s="1">
+      <c r="C81" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D81" s="1">
         <v>31</v>
       </c>
-      <c r="D81" s="1">
+      <c r="F81" s="1">
         <v>785</v>
       </c>
-      <c r="E81" s="1">
+      <c r="G81" s="1">
         <v>2</v>
       </c>
-      <c r="F81" s="1">
+      <c r="H81" s="1">
         <v>96</v>
       </c>
-      <c r="G81" s="1">
+      <c r="I81" s="1">
         <v>300</v>
       </c>
-      <c r="H81" s="1">
+      <c r="J81" s="1">
         <v>335</v>
       </c>
-      <c r="I81" s="1">
+      <c r="K81" s="1">
         <v>750</v>
       </c>
-      <c r="J81" s="1">
+      <c r="L81" s="1">
         <v>57</v>
       </c>
-      <c r="K81" s="1">
+      <c r="M81" s="1">
         <v>266</v>
       </c>
-      <c r="O81" s="1">
+      <c r="Q81" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="A82" s="1">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="A82" s="4">
+        <v>65032</v>
+      </c>
+      <c r="B82" s="1">
         <v>65</v>
       </c>
-      <c r="B82" s="1">
+      <c r="C82" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D82" s="1">
         <v>32</v>
       </c>
-      <c r="D82" s="1">
+      <c r="F82" s="1">
         <v>1344</v>
       </c>
-      <c r="E82" s="1">
+      <c r="G82" s="1">
         <v>5</v>
       </c>
-      <c r="F82" s="1">
+      <c r="H82" s="1">
         <v>116</v>
       </c>
-      <c r="G82" s="1">
+      <c r="I82" s="1">
         <v>249</v>
       </c>
-      <c r="H82" s="1">
+      <c r="J82" s="1">
         <v>313</v>
       </c>
-      <c r="I82" s="1">
+      <c r="K82" s="1">
         <v>1250</v>
       </c>
-      <c r="J82" s="1">
+      <c r="L82" s="1">
         <v>49</v>
       </c>
-      <c r="K82" s="1">
+      <c r="M82" s="1">
         <v>242</v>
       </c>
-      <c r="O82" s="1">
+      <c r="Q82" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="A83" s="1">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="A83" s="4">
+        <v>65033</v>
+      </c>
+      <c r="B83" s="1">
         <v>65</v>
       </c>
-      <c r="B83" s="1">
+      <c r="C83" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D83" s="1">
         <v>33</v>
       </c>
-      <c r="D83" s="1">
+      <c r="F83" s="1">
         <v>1290</v>
       </c>
-      <c r="E83" s="1">
+      <c r="G83" s="1">
         <v>3</v>
       </c>
-      <c r="F83" s="1">
+      <c r="H83" s="1">
         <v>127</v>
       </c>
-      <c r="G83" s="1">
+      <c r="I83" s="1">
         <v>283</v>
       </c>
-      <c r="H83" s="1">
+      <c r="J83" s="1">
         <v>370</v>
       </c>
-      <c r="I83" s="1">
+      <c r="K83" s="1">
         <v>1250</v>
       </c>
-      <c r="J83" s="1">
+      <c r="L83" s="1">
         <v>70</v>
       </c>
-      <c r="K83" s="1">
+      <c r="M83" s="1">
         <v>284</v>
       </c>
-      <c r="O83" s="1">
+      <c r="Q83" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="A84" s="1">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="A84" s="4">
+        <v>65034</v>
+      </c>
+      <c r="B84" s="1">
         <v>65</v>
       </c>
-      <c r="B84" s="1">
+      <c r="C84" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D84" s="1">
         <v>34</v>
       </c>
-      <c r="D84" s="1">
+      <c r="F84" s="1">
         <v>1042</v>
       </c>
-      <c r="E84" s="1">
+      <c r="G84" s="1">
         <v>1</v>
       </c>
-      <c r="F84" s="1">
+      <c r="H84" s="1">
         <v>186</v>
       </c>
-      <c r="G84" s="1">
+      <c r="I84" s="1">
         <v>415</v>
       </c>
-      <c r="H84" s="1">
+      <c r="J84" s="1">
         <v>527</v>
       </c>
-      <c r="I84" s="1">
+      <c r="K84" s="1">
         <v>1000</v>
       </c>
-      <c r="J84" s="1">
+      <c r="L84" s="1">
         <v>111</v>
       </c>
-      <c r="K84" s="1">
+      <c r="M84" s="1">
         <v>404</v>
       </c>
-      <c r="O84" s="1">
+      <c r="Q84" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="A85" s="1">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="A85" s="4">
+        <v>65035</v>
+      </c>
+      <c r="B85" s="1">
         <v>65</v>
       </c>
-      <c r="B85" s="1">
-        <v>35</v>
+      <c r="C85" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="D85" s="1">
+        <v>35</v>
+      </c>
+      <c r="F85" s="1">
         <v>1412</v>
       </c>
-      <c r="E85" s="1">
+      <c r="G85" s="1">
         <v>1</v>
       </c>
-      <c r="F85" s="1">
+      <c r="H85" s="1">
         <v>140</v>
       </c>
-      <c r="G85" s="1">
+      <c r="I85" s="1">
         <v>436</v>
       </c>
-      <c r="H85" s="1">
+      <c r="J85" s="1">
         <v>513</v>
       </c>
-      <c r="I85" s="1">
+      <c r="K85" s="1">
         <v>1350</v>
       </c>
-      <c r="J85" s="1">
+      <c r="L85" s="1">
         <v>40</v>
       </c>
-      <c r="K85" s="1">
+      <c r="M85" s="1">
         <v>453</v>
       </c>
-      <c r="O85" s="1">
+      <c r="Q85" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="A86" s="1">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="A86" s="4">
+        <v>65036</v>
+      </c>
+      <c r="B86" s="1">
         <v>65</v>
       </c>
-      <c r="B86" s="1">
+      <c r="C86" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D86" s="1">
+        <v>36</v>
+      </c>
+      <c r="F86" s="1">
         <v>1359</v>
       </c>
-      <c r="E86" s="1">
+      <c r="G86" s="1">
         <v>3</v>
       </c>
-      <c r="F86" s="1">
+      <c r="H86" s="1">
         <v>125</v>
       </c>
-      <c r="G86" s="1">
+      <c r="I86" s="1">
         <v>360</v>
       </c>
-      <c r="H86" s="1">
+      <c r="J86" s="1">
         <v>525</v>
       </c>
-      <c r="I86" s="1">
+      <c r="K86" s="1">
         <v>1300</v>
       </c>
-      <c r="J86" s="1">
+      <c r="L86" s="1">
         <v>124</v>
       </c>
-      <c r="K86" s="1">
+      <c r="M86" s="1">
         <v>388</v>
       </c>
-      <c r="O86" s="1">
+      <c r="Q86" s="1">
         <v>13</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="A87" s="1">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="A87" s="4">
+        <v>65037</v>
+      </c>
+      <c r="B87" s="1">
         <v>65</v>
       </c>
-      <c r="B87" s="1">
+      <c r="C87" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D87" s="1">
         <v>37</v>
       </c>
-      <c r="D87" s="1">
+      <c r="F87" s="1">
         <v>592</v>
       </c>
-      <c r="E87" s="1">
+      <c r="G87" s="1">
         <v>6</v>
       </c>
-      <c r="F87" s="1">
+      <c r="H87" s="1">
         <v>94</v>
       </c>
-      <c r="G87" s="1">
+      <c r="I87" s="1">
         <v>212</v>
       </c>
-      <c r="H87" s="1">
+      <c r="J87" s="1">
         <v>252</v>
       </c>
-      <c r="I87" s="1">
+      <c r="K87" s="1">
         <v>550</v>
       </c>
-      <c r="J87" s="1">
+      <c r="L87" s="1">
         <v>69</v>
       </c>
-      <c r="K87" s="1">
+      <c r="M87" s="1">
         <v>173</v>
       </c>
-      <c r="O87" s="1">
+      <c r="Q87" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="A88" s="1">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="A88" s="4">
+        <v>65038</v>
+      </c>
+      <c r="B88" s="1">
         <v>65</v>
       </c>
-      <c r="B88" s="1">
+      <c r="C88" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D88" s="1">
         <v>38</v>
       </c>
-      <c r="D88" s="1">
+      <c r="F88" s="1">
         <v>685</v>
       </c>
-      <c r="E88" s="1">
+      <c r="G88" s="1">
         <v>2</v>
       </c>
-      <c r="F88" s="1">
+      <c r="H88" s="1">
         <v>83</v>
       </c>
-      <c r="G88" s="1">
+      <c r="I88" s="1">
         <v>225</v>
       </c>
-      <c r="H88" s="1">
+      <c r="J88" s="1">
         <v>273</v>
       </c>
-      <c r="I88" s="1">
+      <c r="K88" s="1">
         <v>650</v>
       </c>
-      <c r="J88" s="1">
+      <c r="L88" s="1">
         <v>71</v>
       </c>
-      <c r="K88" s="1">
+      <c r="M88" s="1">
         <v>195</v>
       </c>
-      <c r="O88" s="1">
+      <c r="Q88" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="A89" s="1">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.5">
+      <c r="A89" s="4">
+        <v>65039</v>
+      </c>
+      <c r="B89" s="1">
         <v>65</v>
       </c>
-      <c r="B89" s="1">
+      <c r="C89" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D89" s="1">
         <v>39</v>
       </c>
-      <c r="D89" s="1">
+      <c r="F89" s="1">
         <v>393</v>
       </c>
-      <c r="E89" s="1">
+      <c r="G89" s="1">
         <v>1</v>
       </c>
-      <c r="F89" s="1">
+      <c r="H89" s="1">
         <v>75</v>
       </c>
-      <c r="G89" s="1">
+      <c r="I89" s="1">
         <v>164</v>
       </c>
-      <c r="H89" s="1">
+      <c r="J89" s="1">
         <v>193</v>
       </c>
-      <c r="I89" s="1">
+      <c r="K89" s="1">
         <v>400</v>
       </c>
-      <c r="J89" s="1">
+      <c r="L89" s="1">
         <v>49</v>
       </c>
-      <c r="K89" s="1">
+      <c r="M89" s="1">
         <v>141</v>
       </c>
-      <c r="O89" s="1">
+      <c r="Q89" s="1">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A51:B89 D51:K89 O51:O89 A2:O50">
+  <conditionalFormatting sqref="F51:M89 Q51:Q89 B2:Q50 B51:D89">
     <cfRule type="expression" dxfId="0" priority="2">
-      <formula>$B2="ჯამი"</formula>
+      <formula>$D2="ჯამი"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.17" right="0.17" top="0.28999999999999998" bottom="0.75" header="0.2" footer="0.3"/>
@@ -4329,31 +4926,144 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D49C7440-5B75-4EA3-B203-627104662C7D}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A2">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A2" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="9">
-        <v>11</v>
-      </c>
-      <c r="C2" s="9"/>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5">
+        <v>43</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6">
+        <v>44</v>
+      </c>
+      <c r="E6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>65</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7">
+        <v>8</v>
+      </c>
+      <c r="E7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <v>65</v>
+      </c>
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8">
+        <v>41</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
